--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/reinforcement_learning/mol2mol_similarity_rl_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/reinforcement_learning/mol2mol_similarity_rl_generated_optimal.xlsx
@@ -2740,7 +2740,7 @@
         <v>5.467203420787769</v>
       </c>
       <c r="L2" s="3">
-        <v>0.9112486873462657</v>
+        <v>0.9112486873462656</v>
       </c>
       <c r="M2" s="3">
         <v>0.3135618067127634</v>
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>24.96610260009766</v>
+        <v>24.966103</v>
       </c>
       <c r="AB2" s="3">
-        <v>30.07188034057617</v>
+        <v>30.07188</v>
       </c>
       <c r="AC2" s="3">
-        <v>44.14594650268555</v>
+        <v>44.145947</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -2805,55 +2805,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.3464149534702301</v>
+        <v>0.34641495</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.3849506974220276</v>
+        <v>0.3849507</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.7379907369613647</v>
+        <v>0.73799074</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.04763970151543617</v>
+        <v>0.0476397</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.852996826171875</v>
+        <v>0.8529968</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.06335581094026566</v>
+        <v>0.06335581</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.2255509793758392</v>
+        <v>0.22555098</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.3657425343990326</v>
+        <v>0.36574253</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.06939264386892319</v>
+        <v>0.069392644</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.9428127408027649</v>
+        <v>0.94281274</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.999886155128479</v>
+        <v>0.99988616</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.768562912940979</v>
+        <v>0.7685629</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.9410192370414734</v>
+        <v>0.94101924</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8313615918159485</v>
+        <v>0.8313616</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.693534851074219</v>
+        <v>-4.693535</v>
       </c>
       <c r="AV2" s="3">
-        <v>89.08026885986328</v>
+        <v>89.08027</v>
       </c>
       <c r="AW2" s="3">
-        <v>11.20199584960938</v>
+        <v>11.201996</v>
       </c>
       <c r="AX2" s="3">
         <v>456.5900000000002</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>-4.083333015441895</v>
+        <v>-4.083333</v>
       </c>
       <c r="AB3" s="3">
-        <v>-4.834982395172119</v>
+        <v>-4.8349824</v>
       </c>
       <c r="AC3" s="3">
-        <v>40.40203857421875</v>
+        <v>40.40204</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -2986,55 +2986,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.1705893129110336</v>
+        <v>0.17058931</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.6717827916145325</v>
+        <v>0.6717828</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.7626541256904602</v>
+        <v>0.7626541</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.04786701127886772</v>
+        <v>0.04786701</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.827365517616272</v>
+        <v>0.8273655</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.02234799042344093</v>
+        <v>0.02234799</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.04712749272584915</v>
+        <v>0.047127493</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.174581378698349</v>
+        <v>0.17458138</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.07404957711696625</v>
+        <v>0.07404958</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.7154610753059387</v>
+        <v>0.7154611</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9920663833618164</v>
+        <v>0.9920664</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.861157238483429</v>
+        <v>0.86115724</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.6246697306632996</v>
+        <v>0.62466973</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.4933441281318665</v>
+        <v>0.49334413</v>
       </c>
       <c r="AU3" s="3">
-        <v>-5.633456230163574</v>
+        <v>-5.633456</v>
       </c>
       <c r="AV3" s="3">
-        <v>68.32504272460938</v>
+        <v>68.32504</v>
       </c>
       <c r="AW3" s="3">
-        <v>12.52526187896729</v>
+        <v>12.525262</v>
       </c>
       <c r="AX3" s="3">
         <v>472.5930000000004</v>
@@ -3105,7 +3105,7 @@
         <v>1.205100488679826</v>
       </c>
       <c r="M4" s="3">
-        <v>0.3909717546769677</v>
+        <v>0.3909717546769676</v>
       </c>
       <c r="N4" s="3">
         <v>22.02742740728141</v>
@@ -3117,7 +3117,7 @@
         <v>4.794899511320175</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.3909717546769677</v>
+        <v>0.3909717546769676</v>
       </c>
       <c r="R4" s="3">
         <v>2.746602743421294</v>
@@ -3132,7 +3132,7 @@
         <v>5.561204150487031</v>
       </c>
       <c r="V4" s="3">
-        <v>0.3909717546769677</v>
+        <v>0.3909717546769676</v>
       </c>
       <c r="W4" s="3">
         <v>3.053100000000001</v>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>27.36676597595215</v>
+        <v>27.366766</v>
       </c>
       <c r="AB4" s="3">
-        <v>8.899172782897949</v>
+        <v>8.899172999999999</v>
       </c>
       <c r="AC4" s="3">
-        <v>56.92855834960938</v>
+        <v>56.92856</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -3167,55 +3167,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.1182508617639542</v>
+        <v>0.11825086</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.466855525970459</v>
+        <v>0.46685553</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.8780749440193176</v>
+        <v>0.87807494</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.0681447833776474</v>
+        <v>0.06814478</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.8404696583747864</v>
+        <v>0.84046966</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.1501118242740631</v>
+        <v>0.15011182</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.2202935665845871</v>
+        <v>0.22029357</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.6095048785209656</v>
+        <v>0.6095049</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.09269878268241882</v>
+        <v>0.09269877999999999</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.9416144490242004</v>
+        <v>0.94161445</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9995377659797668</v>
+        <v>0.99953777</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.8356820940971375</v>
+        <v>0.8356821</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.8891841769218445</v>
+        <v>0.8891842</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.8300701975822449</v>
+        <v>0.8300702</v>
       </c>
       <c r="AU4" s="3">
-        <v>-5.385392189025879</v>
+        <v>-5.385392</v>
       </c>
       <c r="AV4" s="3">
-        <v>86.55036926269531</v>
+        <v>86.55037</v>
       </c>
       <c r="AW4" s="3">
-        <v>11.61265182495117</v>
+        <v>11.612652</v>
       </c>
       <c r="AX4" s="3">
         <v>485.5880000000004</v>
@@ -3330,13 +3330,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>18.61470222473145</v>
+        <v>18.614702</v>
       </c>
       <c r="AB5" s="3">
-        <v>5.730818271636963</v>
+        <v>5.7308183</v>
       </c>
       <c r="AC5" s="3">
-        <v>58.93181610107422</v>
+        <v>58.931816</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -3348,55 +3348,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.1409033536911011</v>
+        <v>0.14090335</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.511079728603363</v>
+        <v>0.5110797</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.8841705322265625</v>
+        <v>0.88417053</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.09742866456508636</v>
+        <v>0.097428665</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.8027888536453247</v>
+        <v>0.80278885</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.07023058831691742</v>
+        <v>0.07023059</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.1908525973558426</v>
+        <v>0.1908526</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.5615813136100769</v>
+        <v>0.5615812999999999</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.09687140583992004</v>
+        <v>0.09687140599999999</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.8482539057731628</v>
+        <v>0.8482539</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9975885152816772</v>
+        <v>0.9975885</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.8236236572265625</v>
+        <v>0.82362366</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.7345705628395081</v>
+        <v>0.73457056</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.7775531411170959</v>
+        <v>0.77755314</v>
       </c>
       <c r="AU5" s="3">
-        <v>-5.474039554595947</v>
+        <v>-5.4740396</v>
       </c>
       <c r="AV5" s="3">
-        <v>86.53185272216797</v>
+        <v>86.53185000000001</v>
       </c>
       <c r="AW5" s="3">
-        <v>11.29617881774902</v>
+        <v>11.296179</v>
       </c>
       <c r="AX5" s="3">
         <v>471.5610000000003</v>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>21.06924438476562</v>
+        <v>21.069244</v>
       </c>
       <c r="AB6" s="3">
-        <v>7.316725254058838</v>
+        <v>7.3167253</v>
       </c>
       <c r="AC6" s="3">
-        <v>50.41398620605469</v>
+        <v>50.413986</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -3529,55 +3529,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.1413627117872238</v>
+        <v>0.14136271</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.4205498695373535</v>
+        <v>0.42054987</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.9040927886962891</v>
+        <v>0.9040928</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.09064941108226776</v>
+        <v>0.09064941</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.7514630556106567</v>
+        <v>0.75146306</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.1254187822341919</v>
+        <v>0.12541878</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.2258846461772919</v>
+        <v>0.22588465</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.6337138414382935</v>
+        <v>0.63371384</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.06155655533075333</v>
+        <v>0.061556555</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.893102765083313</v>
+        <v>0.89310277</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9988150596618652</v>
+        <v>0.99881506</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.8253436088562012</v>
+        <v>0.8253436</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.8274537324905396</v>
+        <v>0.82745373</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.8134618997573853</v>
+        <v>0.8134619</v>
       </c>
       <c r="AU6" s="3">
-        <v>-5.153609275817871</v>
+        <v>-5.1536093</v>
       </c>
       <c r="AV6" s="3">
-        <v>89.10317993164062</v>
+        <v>89.10317999999999</v>
       </c>
       <c r="AW6" s="3">
-        <v>8.630931854248047</v>
+        <v>8.630932</v>
       </c>
       <c r="AX6" s="3">
         <v>439.5190000000001</v>
@@ -3654,7 +3654,7 @@
         <v>28.58106516888546</v>
       </c>
       <c r="O7" s="3">
-        <v>20.69383755035367</v>
+        <v>20.69383755035368</v>
       </c>
       <c r="P7" s="3">
         <v>4.722803853682293</v>
@@ -3669,7 +3669,7 @@
         <v>143.8963697335989</v>
       </c>
       <c r="T7" s="3">
-        <v>3.841950162453619</v>
+        <v>3.841950162453618</v>
       </c>
       <c r="U7" s="3">
         <v>5.603657544910967</v>
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>17.11203384399414</v>
+        <v>17.112034</v>
       </c>
       <c r="AB7" s="3">
-        <v>6.442348480224609</v>
+        <v>6.4423485</v>
       </c>
       <c r="AC7" s="3">
-        <v>45.9471321105957</v>
+        <v>45.947132</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -3710,55 +3710,55 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.2348897904157639</v>
+        <v>0.23488979</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.3777771890163422</v>
+        <v>0.3777772</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.9140210151672363</v>
+        <v>0.914021</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.0774558037519455</v>
+        <v>0.077455804</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.6477356553077698</v>
+        <v>0.64773566</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.07433494180440903</v>
+        <v>0.07433494</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.1458786427974701</v>
+        <v>0.14587864</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.443953812122345</v>
+        <v>0.4439538</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.03482164070010185</v>
+        <v>0.03482164</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.7904225587844849</v>
+        <v>0.79042256</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.997406005859375</v>
+        <v>0.997406</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.8409801721572876</v>
+        <v>0.8409802</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.7810645699501038</v>
+        <v>0.78106457</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.607813835144043</v>
+        <v>0.60781384</v>
       </c>
       <c r="AU7" s="3">
-        <v>-5.086916446685791</v>
+        <v>-5.0869164</v>
       </c>
       <c r="AV7" s="3">
-        <v>87.78946685791016</v>
+        <v>87.78946999999999</v>
       </c>
       <c r="AW7" s="3">
-        <v>6.922562599182129</v>
+        <v>6.9225626</v>
       </c>
       <c r="AX7" s="3">
         <v>425.4920000000002</v>
@@ -3850,7 +3850,7 @@
         <v>115.1849850340321</v>
       </c>
       <c r="T8" s="3">
-        <v>3.938604129783164</v>
+        <v>3.938604129783165</v>
       </c>
       <c r="U8" s="3">
         <v>5.572182726223377</v>
@@ -3873,13 +3873,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>17.78740882873535</v>
+        <v>17.787409</v>
       </c>
       <c r="AB8" s="3">
-        <v>1.984968900680542</v>
+        <v>1.9849689</v>
       </c>
       <c r="AC8" s="3">
-        <v>42.25897598266602</v>
+        <v>42.258976</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -3891,55 +3891,55 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.125828742980957</v>
+        <v>0.12582874</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.4581222534179688</v>
+        <v>0.45812225</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.8723117113113403</v>
+        <v>0.8723117</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.09618829190731049</v>
+        <v>0.09618829</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.6371511220932007</v>
+        <v>0.6371511</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.04952653124928474</v>
+        <v>0.04952653</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.0893918052315712</v>
+        <v>0.089391805</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.3551625609397888</v>
+        <v>0.35516256</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.06723065674304962</v>
+        <v>0.06723066</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.6644631028175354</v>
+        <v>0.6644631</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.993190586566925</v>
+        <v>0.9931906</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.8410142660140991</v>
+        <v>0.84101427</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.5999529957771301</v>
+        <v>0.599953</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.5326551795005798</v>
+        <v>0.5326552</v>
       </c>
       <c r="AU8" s="3">
-        <v>-5.559248924255371</v>
+        <v>-5.559249</v>
       </c>
       <c r="AV8" s="3">
-        <v>81.04439544677734</v>
+        <v>81.04439499999999</v>
       </c>
       <c r="AW8" s="3">
-        <v>8.659089088439941</v>
+        <v>8.659089</v>
       </c>
       <c r="AX8" s="3">
         <v>457.5340000000002</v>
@@ -3954,7 +3954,7 @@
         <v>4</v>
       </c>
       <c r="BB8" s="3">
-        <v>3.389263598193239</v>
+        <v>3.389263598193238</v>
       </c>
       <c r="BC8" s="3">
         <v>0.734526266867418</v>
@@ -4001,7 +4001,7 @@
         <v>0.5961650780225352</v>
       </c>
       <c r="J9" s="3">
-        <v>3.946072662383627</v>
+        <v>3.946072662383626</v>
       </c>
       <c r="K9" s="3">
         <v>5.403834921977465</v>
@@ -4054,13 +4054,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>12.61844635009766</v>
+        <v>12.618446</v>
       </c>
       <c r="AB9" s="3">
-        <v>3.079665660858154</v>
+        <v>3.0796657</v>
       </c>
       <c r="AC9" s="3">
-        <v>64.01219940185547</v>
+        <v>64.01220000000001</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -4072,55 +4072,55 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.219668909907341</v>
+        <v>0.21966891</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.5951234102249146</v>
+        <v>0.5951234</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.906309962272644</v>
+        <v>0.90630996</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.08913515508174896</v>
+        <v>0.08913515499999999</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.8161934614181519</v>
+        <v>0.81619346</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.09744378924369812</v>
+        <v>0.09744379</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.1833284795284271</v>
+        <v>0.18332848</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.4187563061714172</v>
+        <v>0.4187563</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.08148814737796783</v>
+        <v>0.08148815</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.7457108497619629</v>
+        <v>0.74571085</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.9973219037055969</v>
+        <v>0.9973219</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.8388110399246216</v>
+        <v>0.83881104</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.739662230014801</v>
+        <v>0.73966223</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.6621659994125366</v>
+        <v>0.662166</v>
       </c>
       <c r="AU9" s="3">
-        <v>-5.377617359161377</v>
+        <v>-5.3776174</v>
       </c>
       <c r="AV9" s="3">
-        <v>88.47909545898438</v>
+        <v>88.479095</v>
       </c>
       <c r="AW9" s="3">
-        <v>11.93954849243164</v>
+        <v>11.9395485</v>
       </c>
       <c r="AX9" s="3">
         <v>441.5350000000002</v>
@@ -4188,10 +4188,10 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L10" s="3">
-        <v>1.122505373766745</v>
+        <v>1.122505373766744</v>
       </c>
       <c r="M10" s="3">
-        <v>0.3267701779547809</v>
+        <v>0.3267701779547808</v>
       </c>
       <c r="N10" s="3">
         <v>17.03939254360327</v>
@@ -4203,7 +4203,7 @@
         <v>4.877494626233256</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.3267701779547809</v>
+        <v>0.3267701779547808</v>
       </c>
       <c r="R10" s="3">
         <v>3.034141460365158</v>
@@ -4218,7 +4218,7 @@
         <v>5.517964175024626</v>
       </c>
       <c r="V10" s="3">
-        <v>0.3267701779547809</v>
+        <v>0.3267701779547808</v>
       </c>
       <c r="W10" s="3">
         <v>2.3677</v>
@@ -4227,7 +4227,7 @@
         <v>-3.999814735548187</v>
       </c>
       <c r="Y10" s="3">
-        <v>0.0001000426678166251</v>
+        <v>0.0001000426678166</v>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>-6.54572582244873</v>
+        <v>-6.545726</v>
       </c>
       <c r="AB10" s="3">
-        <v>3.294821500778198</v>
+        <v>3.2948215</v>
       </c>
       <c r="AC10" s="3">
-        <v>47.54159164428711</v>
+        <v>47.54159</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -4253,55 +4253,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.2892054617404938</v>
+        <v>0.28920546</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.6124958992004395</v>
+        <v>0.6124959</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.2789924740791321</v>
+        <v>0.27899247</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.07092592120170593</v>
+        <v>0.07092592</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.9047673344612122</v>
+        <v>0.90476733</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.1110580712556839</v>
+        <v>0.11105807</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.1230947002768517</v>
+        <v>0.1230947</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.08251931518316269</v>
+        <v>0.082519315</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.5067145228385925</v>
+        <v>0.5067145</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.705535888671875</v>
+        <v>0.7055359</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9995586276054382</v>
+        <v>0.9995586</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.7140973210334778</v>
+        <v>0.7140973</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.9144508242607117</v>
+        <v>0.9144508</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.5570255517959595</v>
+        <v>0.55702555</v>
       </c>
       <c r="AU10" s="3">
-        <v>-4.829124450683594</v>
+        <v>-4.8291245</v>
       </c>
       <c r="AV10" s="3">
-        <v>48.14134216308594</v>
+        <v>48.141342</v>
       </c>
       <c r="AW10" s="3">
-        <v>13.46353912353516</v>
+        <v>13.463539</v>
       </c>
       <c r="AX10" s="3">
         <v>366.5090000000002</v>
@@ -4408,7 +4408,7 @@
         <v>-3.621357913772641</v>
       </c>
       <c r="Y11" s="3">
-        <v>0.000239134417299762</v>
+        <v>0.0002391344172997</v>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>-8.814027786254883</v>
+        <v>-8.814028</v>
       </c>
       <c r="AB11" s="3">
-        <v>2.088809967041016</v>
+        <v>2.08881</v>
       </c>
       <c r="AC11" s="3">
-        <v>46.66522216796875</v>
+        <v>46.665222</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -4434,55 +4434,55 @@
         <v>1</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.3678248524665833</v>
+        <v>0.36782485</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.6005585193634033</v>
+        <v>0.6005585</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.2948376536369324</v>
+        <v>0.29483765</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.08644183725118637</v>
+        <v>0.08644184000000001</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.8860233426094055</v>
+        <v>0.88602334</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.1050174608826637</v>
+        <v>0.10501746</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.1130646914243698</v>
+        <v>0.11306469</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.06489381939172745</v>
+        <v>0.06489382</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.4695448875427246</v>
+        <v>0.4695449</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.6544495224952698</v>
+        <v>0.6544495</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9991741180419922</v>
+        <v>0.9991741</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.7290127277374268</v>
+        <v>0.7290127</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.8918673396110535</v>
+        <v>0.89186734</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.4496602118015289</v>
+        <v>0.4496602</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.788086414337158</v>
+        <v>-4.7880864</v>
       </c>
       <c r="AV11" s="3">
-        <v>49.35315322875977</v>
+        <v>49.353153</v>
       </c>
       <c r="AW11" s="3">
-        <v>12.35941505432129</v>
+        <v>12.359415</v>
       </c>
       <c r="AX11" s="3">
         <v>352.4820000000001</v>
@@ -4491,7 +4491,7 @@
         <v>1.9776</v>
       </c>
       <c r="AZ11" s="3">
-        <v>0.4719213574328682</v>
+        <v>0.4719213574328681</v>
       </c>
       <c r="BA11" s="3">
         <v>4</v>
@@ -4550,7 +4550,7 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L12" s="3">
-        <v>1.091210780231489</v>
+        <v>1.091210780231488</v>
       </c>
       <c r="M12" s="3">
         <v>0.3620215088585307</v>
@@ -4562,13 +4562,13 @@
         <v>12.61993144552603</v>
       </c>
       <c r="P12" s="3">
-        <v>4.908789219768511</v>
+        <v>4.908789219768512</v>
       </c>
       <c r="Q12" s="3">
         <v>0.3620215088585307</v>
       </c>
       <c r="R12" s="3">
-        <v>2.407956421211619</v>
+        <v>2.40795642121162</v>
       </c>
       <c r="S12" s="3">
         <v>63.20812935853365</v>
@@ -4589,7 +4589,7 @@
         <v>-3.624809459338599</v>
       </c>
       <c r="Y12" s="3">
-        <v>0.0002372414341146504</v>
+        <v>0.0002372414341146</v>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>-1.574264883995056</v>
+        <v>-1.5742649</v>
       </c>
       <c r="AB12" s="3">
-        <v>6.70600414276123</v>
+        <v>6.706004</v>
       </c>
       <c r="AC12" s="3">
-        <v>40.21139526367188</v>
+        <v>40.211395</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -4615,55 +4615,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.2724735140800476</v>
+        <v>0.2724735</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.567768931388855</v>
+        <v>0.5677689299999999</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.2823957800865173</v>
+        <v>0.28239578</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.07963231950998306</v>
+        <v>0.07963232000000001</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.8710237741470337</v>
+        <v>0.8710238</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.1062963381409645</v>
+        <v>0.10629634</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.1266083717346191</v>
+        <v>0.12660837</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.08495347201824188</v>
+        <v>0.08495347</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.4344733655452728</v>
+        <v>0.43447337</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.6483556628227234</v>
+        <v>0.64835566</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9995330572128296</v>
+        <v>0.99953306</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.7362068891525269</v>
+        <v>0.7362069</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.908692479133606</v>
+        <v>0.9086925</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.3971052169799805</v>
+        <v>0.39710522</v>
       </c>
       <c r="AU12" s="3">
-        <v>-4.745772361755371</v>
+        <v>-4.7457724</v>
       </c>
       <c r="AV12" s="3">
-        <v>50.065673828125</v>
+        <v>50.065674</v>
       </c>
       <c r="AW12" s="3">
-        <v>10.76571369171143</v>
+        <v>10.765714</v>
       </c>
       <c r="AX12" s="3">
         <v>352.4820000000002</v>
@@ -4770,7 +4770,7 @@
         <v>-3.862046701765551</v>
       </c>
       <c r="Y13" s="3">
-        <v>0.0001373894225642657</v>
+        <v>0.0001373894225642</v>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>8.31247615814209</v>
+        <v>8.312476</v>
       </c>
       <c r="AB13" s="3">
-        <v>23.92286682128906</v>
+        <v>23.922867</v>
       </c>
       <c r="AC13" s="3">
-        <v>43.406982421875</v>
+        <v>43.406982</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -4796,55 +4796,55 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.2393747866153717</v>
+        <v>0.23937479</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.6658600568771362</v>
+        <v>0.66586006</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.6856173276901245</v>
+        <v>0.6856173</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.06390014290809631</v>
+        <v>0.06390013999999999</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.8735777139663696</v>
+        <v>0.8735777</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.1395732462406158</v>
+        <v>0.13957325</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.08888677507638931</v>
+        <v>0.088886775</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.1830259561538696</v>
+        <v>0.18302596</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.1041961908340454</v>
+        <v>0.10419619</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.9115807414054871</v>
+        <v>0.91158074</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9996579885482788</v>
+        <v>0.999658</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.8682630658149719</v>
+        <v>0.86826307</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.886378288269043</v>
+        <v>0.8863783</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.4177024960517883</v>
+        <v>0.4177025</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.853062629699707</v>
+        <v>-4.8530626</v>
       </c>
       <c r="AV13" s="3">
-        <v>64.49317932128906</v>
+        <v>64.49318</v>
       </c>
       <c r="AW13" s="3">
-        <v>14.42065715789795</v>
+        <v>14.420657</v>
       </c>
       <c r="AX13" s="3">
         <v>389.5030000000002</v>
@@ -4930,7 +4930,7 @@
         <v>0.4013141379778254</v>
       </c>
       <c r="R14" s="3">
-        <v>2.580718495724783</v>
+        <v>2.580718495724782</v>
       </c>
       <c r="S14" s="3">
         <v>96.58107949592166</v>
@@ -4951,7 +4951,7 @@
         <v>-3.862046701765551</v>
       </c>
       <c r="Y14" s="3">
-        <v>0.0001373894225642656</v>
+        <v>0.0001373894225642</v>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
@@ -4959,13 +4959,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>12.68989753723145</v>
+        <v>12.689898</v>
       </c>
       <c r="AB14" s="3">
-        <v>30.11833572387695</v>
+        <v>30.118336</v>
       </c>
       <c r="AC14" s="3">
-        <v>50.95757293701172</v>
+        <v>50.957573</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -4977,55 +4977,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.3580076098442078</v>
+        <v>0.3580076</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.6448127031326294</v>
+        <v>0.6448127</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.6861821413040161</v>
+        <v>0.68618214</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.09838350862264633</v>
+        <v>0.09838350999999999</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.7963563203811646</v>
+        <v>0.7963563</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.1356841921806335</v>
+        <v>0.13568419</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.0600593313574791</v>
+        <v>0.06005933</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.1015919595956802</v>
+        <v>0.10159196</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.09456886351108551</v>
+        <v>0.09456886</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.6564647555351257</v>
+        <v>0.65646476</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9982963800430298</v>
+        <v>0.9982964</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.8935096859931946</v>
+        <v>0.8935097</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.8746302723884583</v>
+        <v>0.8746303</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.3130467534065247</v>
+        <v>0.31304675</v>
       </c>
       <c r="AU14" s="3">
-        <v>-4.616786956787109</v>
+        <v>-4.616787</v>
       </c>
       <c r="AV14" s="3">
-        <v>74.89380645751953</v>
+        <v>74.89381</v>
       </c>
       <c r="AW14" s="3">
-        <v>15.08733558654785</v>
+        <v>15.087336</v>
       </c>
       <c r="AX14" s="3">
         <v>389.5030000000002</v>
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>28.76948547363281</v>
+        <v>28.769485</v>
       </c>
       <c r="AB15" s="3">
-        <v>30.2982234954834</v>
+        <v>30.298223</v>
       </c>
       <c r="AC15" s="3">
-        <v>57.05619049072266</v>
+        <v>57.05619</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -5158,55 +5158,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.2785089612007141</v>
+        <v>0.27850896</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.3208361864089966</v>
+        <v>0.3208362</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.8894662857055664</v>
+        <v>0.8894663</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.06087876111268997</v>
+        <v>0.06087876</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.831378161907196</v>
+        <v>0.83137816</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.4018661379814148</v>
+        <v>0.40186614</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.4357124269008636</v>
+        <v>0.43571243</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.6800966262817383</v>
+        <v>0.6800966000000001</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.06176295131444931</v>
+        <v>0.06176295</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.9744901657104492</v>
+        <v>0.97449017</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9999784231185913</v>
+        <v>0.9999784</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.8366035223007202</v>
+        <v>0.8366035000000001</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.9628682136535645</v>
+        <v>0.9628682</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.7784509062767029</v>
+        <v>0.7784508999999999</v>
       </c>
       <c r="AU15" s="3">
-        <v>-4.719651699066162</v>
+        <v>-4.7196517</v>
       </c>
       <c r="AV15" s="3">
-        <v>96.51109313964844</v>
+        <v>96.51109</v>
       </c>
       <c r="AW15" s="3">
-        <v>9.312528610229492</v>
+        <v>9.312529</v>
       </c>
       <c r="AX15" s="3">
         <v>411.5090000000002</v>
@@ -5277,7 +5277,7 @@
         <v>1.204463493590013</v>
       </c>
       <c r="M16" s="3">
-        <v>0.4054288858010595</v>
+        <v>0.4054288858010594</v>
       </c>
       <c r="N16" s="3">
         <v>23.04068158531356</v>
@@ -5289,7 +5289,7 @@
         <v>4.795536506409987</v>
       </c>
       <c r="Q16" s="3">
-        <v>0.4054288858010595</v>
+        <v>0.4054288858010594</v>
       </c>
       <c r="R16" s="3">
         <v>2.569347686776966</v>
@@ -5304,7 +5304,7 @@
         <v>5.590177122580064</v>
       </c>
       <c r="V16" s="3">
-        <v>0.4054288858010595</v>
+        <v>0.4054288858010594</v>
       </c>
       <c r="W16" s="3">
         <v>3.038800000000001</v>
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>12.86490345001221</v>
+        <v>12.864903</v>
       </c>
       <c r="AB16" s="3">
-        <v>4.243157863616943</v>
+        <v>4.243158</v>
       </c>
       <c r="AC16" s="3">
-        <v>61.92736053466797</v>
+        <v>61.92736</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -5339,55 +5339,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.2191758155822754</v>
+        <v>0.21917582</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.6002016067504883</v>
+        <v>0.6002016</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.9018386006355286</v>
+        <v>0.9018386</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.08756998181343079</v>
+        <v>0.08756998000000001</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.8499458432197571</v>
+        <v>0.84994584</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.1537113934755325</v>
+        <v>0.1537114</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.2473582029342651</v>
+        <v>0.2473582</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.5446519255638123</v>
+        <v>0.5446519</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.1063937097787857</v>
+        <v>0.10639371</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.8695241808891296</v>
+        <v>0.8695242</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.9986016154289246</v>
+        <v>0.9986016</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.8282780647277832</v>
+        <v>0.82827806</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.7916744947433472</v>
+        <v>0.7916744999999999</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.7248057126998901</v>
+        <v>0.7248057</v>
       </c>
       <c r="AU16" s="3">
-        <v>-5.372579097747803</v>
+        <v>-5.372579</v>
       </c>
       <c r="AV16" s="3">
-        <v>88.33853912353516</v>
+        <v>88.33853999999999</v>
       </c>
       <c r="AW16" s="3">
-        <v>11.47494697570801</v>
+        <v>11.474947</v>
       </c>
       <c r="AX16" s="3">
         <v>441.5350000000002</v>
@@ -5458,19 +5458,19 @@
         <v>1.199457191714284</v>
       </c>
       <c r="M17" s="3">
-        <v>0.3742790068962442</v>
+        <v>0.3742790068962441</v>
       </c>
       <c r="N17" s="3">
         <v>21.28288045358353</v>
       </c>
       <c r="O17" s="3">
-        <v>12.95297527016371</v>
+        <v>12.9529752701637</v>
       </c>
       <c r="P17" s="3">
         <v>4.800542808285716</v>
       </c>
       <c r="Q17" s="3">
-        <v>0.3742790068962442</v>
+        <v>0.3742790068962441</v>
       </c>
       <c r="R17" s="3">
         <v>2.923279481018798</v>
@@ -5485,7 +5485,7 @@
         <v>5.534129661802355</v>
       </c>
       <c r="V17" s="3">
-        <v>0.3742790068962442</v>
+        <v>0.3742790068962441</v>
       </c>
       <c r="W17" s="3">
         <v>2.657900000000001</v>
@@ -5502,13 +5502,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>28.94391822814941</v>
+        <v>28.943918</v>
       </c>
       <c r="AB17" s="3">
-        <v>17.92710494995117</v>
+        <v>17.927105</v>
       </c>
       <c r="AC17" s="3">
-        <v>40.13547134399414</v>
+        <v>40.13547</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -5520,55 +5520,55 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.2008058279752731</v>
+        <v>0.20080583</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.4130944311618805</v>
+        <v>0.41309443</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.8726428151130676</v>
+        <v>0.8726428000000001</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.05753488466143608</v>
+        <v>0.057534885</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.8633538484573364</v>
+        <v>0.86335385</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.2062399834394455</v>
+        <v>0.20623998</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.3947989344596863</v>
+        <v>0.39479893</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.7073718309402466</v>
+        <v>0.70737183</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.09040853381156921</v>
+        <v>0.090408534</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.9699393510818481</v>
+        <v>0.96993935</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9998747110366821</v>
+        <v>0.9998747</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.8315909504890442</v>
+        <v>0.8315909500000001</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.9254981875419617</v>
+        <v>0.9254982</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.808219313621521</v>
+        <v>0.8082193</v>
       </c>
       <c r="AU17" s="3">
-        <v>-5.133326530456543</v>
+        <v>-5.1333265</v>
       </c>
       <c r="AV17" s="3">
-        <v>91.224853515625</v>
+        <v>91.22485</v>
       </c>
       <c r="AW17" s="3">
-        <v>7.83324146270752</v>
+        <v>7.8332415</v>
       </c>
       <c r="AX17" s="3">
         <v>430.5080000000002</v>
@@ -5639,7 +5639,7 @@
         <v>1.057934537427792</v>
       </c>
       <c r="M18" s="3">
-        <v>0.291282580839816</v>
+        <v>0.2912825808398159</v>
       </c>
       <c r="N18" s="3">
         <v>14.08760190468783</v>
@@ -5651,7 +5651,7 @@
         <v>4.942065462572208</v>
       </c>
       <c r="Q18" s="3">
-        <v>0.291282580839816</v>
+        <v>0.2912825808398159</v>
       </c>
       <c r="R18" s="3">
         <v>3.069168123705543</v>
@@ -5666,7 +5666,7 @@
         <v>5.512979321018247</v>
       </c>
       <c r="V18" s="3">
-        <v>0.291282580839816</v>
+        <v>0.2912825808398159</v>
       </c>
       <c r="W18" s="3">
         <v>3.147900000000002</v>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>2.874259948730469</v>
+        <v>2.87426</v>
       </c>
       <c r="AB18" s="3">
-        <v>10.27583408355713</v>
+        <v>10.275834</v>
       </c>
       <c r="AC18" s="3">
-        <v>44.11923217773438</v>
+        <v>44.119232</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -5701,55 +5701,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.3012849688529968</v>
+        <v>0.30128497</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.5903719663619995</v>
+        <v>0.59037197</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.2250855416059494</v>
+        <v>0.22508554</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.05080010369420052</v>
+        <v>0.050800104</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.9012715220451355</v>
+        <v>0.9012715</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.0174088291823864</v>
+        <v>0.01740883</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.03744377195835114</v>
+        <v>0.037443772</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.0287805013358593</v>
+        <v>0.028780501</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.3926112055778503</v>
+        <v>0.3926112</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.4730033874511719</v>
+        <v>0.4730034</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9989698529243469</v>
+        <v>0.99896985</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.6966899633407593</v>
+        <v>0.6966899600000001</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.8672643899917603</v>
+        <v>0.8672644</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.5419316291809082</v>
+        <v>0.5419316</v>
       </c>
       <c r="AU18" s="3">
-        <v>-5.026196956634521</v>
+        <v>-5.026197</v>
       </c>
       <c r="AV18" s="3">
-        <v>46.88035583496094</v>
+        <v>46.880356</v>
       </c>
       <c r="AW18" s="3">
-        <v>14.84892845153809</v>
+        <v>14.848928</v>
       </c>
       <c r="AX18" s="3">
         <v>394.5630000000003</v>
@@ -5838,7 +5838,7 @@
         <v>2.655577021579445</v>
       </c>
       <c r="S19" s="3">
-        <v>42.28525260807019</v>
+        <v>42.2852526080702</v>
       </c>
       <c r="T19" s="3">
         <v>4.373811070631112</v>
@@ -5864,13 +5864,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>20.70138549804688</v>
+        <v>20.701385</v>
       </c>
       <c r="AB19" s="3">
-        <v>22.91081619262695</v>
+        <v>22.910816</v>
       </c>
       <c r="AC19" s="3">
-        <v>48.15154266357422</v>
+        <v>48.151543</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -5882,55 +5882,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.2779860496520996</v>
+        <v>0.27798605</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.6890163421630859</v>
+        <v>0.68901634</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.3792323172092438</v>
+        <v>0.37923232</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.08449985086917877</v>
+        <v>0.08449985</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.9492031335830688</v>
+        <v>0.94920313</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.08677329868078232</v>
+        <v>0.0867733</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.2208823263645172</v>
+        <v>0.22088233</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.170470118522644</v>
+        <v>0.17047012</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.5715908408164978</v>
+        <v>0.57159084</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.8111069798469543</v>
+        <v>0.811107</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9994970560073853</v>
+        <v>0.99949706</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.6690660715103149</v>
+        <v>0.6690661</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.9248945116996765</v>
+        <v>0.9248945</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.8146342039108276</v>
+        <v>0.8146342</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.78680944442749</v>
+        <v>-4.7868094</v>
       </c>
       <c r="AV19" s="3">
-        <v>66.96466827392578</v>
+        <v>66.96467</v>
       </c>
       <c r="AW19" s="3">
-        <v>14.68597412109375</v>
+        <v>14.685974</v>
       </c>
       <c r="AX19" s="3">
         <v>394.5630000000003</v>
@@ -6045,13 +6045,13 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>1.35764467716217</v>
+        <v>1.3576447</v>
       </c>
       <c r="AB20" s="3">
-        <v>11.35908889770508</v>
+        <v>11.359089</v>
       </c>
       <c r="AC20" s="3">
-        <v>40.95880126953125</v>
+        <v>40.9588</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -6063,55 +6063,55 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.6213773488998413</v>
+        <v>0.6213773500000001</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.6324020624160767</v>
+        <v>0.63240206</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.326662540435791</v>
+        <v>0.32666254</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.07832857221364975</v>
+        <v>0.07832857</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.8426512479782104</v>
+        <v>0.84265125</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.02755588851869106</v>
+        <v>0.027555889</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.07026384025812149</v>
+        <v>0.07026383999999999</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.03468775376677513</v>
+        <v>0.034687754</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.278967946767807</v>
+        <v>0.27896795</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.3763377964496613</v>
+        <v>0.3763378</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.9987371563911438</v>
+        <v>0.99873716</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.7757606506347656</v>
+        <v>0.7757606500000001</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.8586103320121765</v>
+        <v>0.85861033</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.384433776140213</v>
+        <v>0.38443378</v>
       </c>
       <c r="AU20" s="3">
-        <v>-4.941065788269043</v>
+        <v>-4.941066</v>
       </c>
       <c r="AV20" s="3">
-        <v>47.20691299438477</v>
+        <v>47.206913</v>
       </c>
       <c r="AW20" s="3">
-        <v>13.28350257873535</v>
+        <v>13.283503</v>
       </c>
       <c r="AX20" s="3">
         <v>396.5350000000004</v>
@@ -6182,7 +6182,7 @@
         <v>1.111664212664238</v>
       </c>
       <c r="M21" s="3">
-        <v>0.3125928389532384</v>
+        <v>0.3125928389532383</v>
       </c>
       <c r="N21" s="3">
         <v>16.32887080518903</v>
@@ -6194,7 +6194,7 @@
         <v>4.888335787335762</v>
       </c>
       <c r="Q21" s="3">
-        <v>0.3125928389532384</v>
+        <v>0.3125928389532383</v>
       </c>
       <c r="R21" s="3">
         <v>3.154875665943301</v>
@@ -6209,7 +6209,7 @@
         <v>5.50101775168411</v>
       </c>
       <c r="V21" s="3">
-        <v>0.3125928389532384</v>
+        <v>0.3125928389532383</v>
       </c>
       <c r="W21" s="3">
         <v>2.757800000000001</v>
@@ -6226,13 +6226,13 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>-2.322286605834961</v>
+        <v>-2.3222866</v>
       </c>
       <c r="AB21" s="3">
-        <v>7.64590311050415</v>
+        <v>7.645903</v>
       </c>
       <c r="AC21" s="3">
-        <v>48.58298110961914</v>
+        <v>48.58298</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -6244,55 +6244,55 @@
         <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.3027557730674744</v>
+        <v>0.30275577</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.6837781667709351</v>
+        <v>0.68377817</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.3125993013381958</v>
+        <v>0.3125993</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.07063645124435425</v>
+        <v>0.07063645</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.9334524869918823</v>
+        <v>0.9334525</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.1096007078886032</v>
+        <v>0.10960071</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.1287549436092377</v>
+        <v>0.12875494</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.08793148398399353</v>
+        <v>0.087931484</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.5680161714553833</v>
+        <v>0.5680162</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.6939274072647095</v>
+        <v>0.6939274</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9993858337402344</v>
+        <v>0.99938583</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.685988187789917</v>
+        <v>0.6859882</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.9007071256637573</v>
+        <v>0.9007071</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.7121826410293579</v>
+        <v>0.71218264</v>
       </c>
       <c r="AU21" s="3">
-        <v>-4.863816261291504</v>
+        <v>-4.8638163</v>
       </c>
       <c r="AV21" s="3">
-        <v>53.9608268737793</v>
+        <v>53.960827</v>
       </c>
       <c r="AW21" s="3">
-        <v>14.65973472595215</v>
+        <v>14.659735</v>
       </c>
       <c r="AX21" s="3">
         <v>380.5360000000003</v>
@@ -6393,7 +6393,7 @@
         <v>0.3130639613010305</v>
       </c>
       <c r="W22" s="3">
-        <v>2.756200000000002</v>
+        <v>2.756200000000001</v>
       </c>
       <c r="X22" s="3">
         <v>-4.377345103911106</v>
@@ -6407,13 +6407,13 @@
         </is>
       </c>
       <c r="AA22" s="3">
-        <v>17.39614868164062</v>
+        <v>17.396149</v>
       </c>
       <c r="AB22" s="3">
-        <v>20.66770362854004</v>
+        <v>20.667704</v>
       </c>
       <c r="AC22" s="3">
-        <v>45.78908920288086</v>
+        <v>45.78909</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -6425,61 +6425,61 @@
         <v>1</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.3398615717887878</v>
+        <v>0.33986157</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.6791695356369019</v>
+        <v>0.67916954</v>
       </c>
       <c r="AI22" s="3">
-        <v>0.3934739232063293</v>
+        <v>0.39347392</v>
       </c>
       <c r="AJ22" s="3">
-        <v>0.09107197821140289</v>
+        <v>0.09107198</v>
       </c>
       <c r="AK22" s="3">
-        <v>0.9413973093032837</v>
+        <v>0.9413973</v>
       </c>
       <c r="AL22" s="3">
-        <v>0.09287159889936447</v>
+        <v>0.0928716</v>
       </c>
       <c r="AM22" s="3">
-        <v>0.2054514437913895</v>
+        <v>0.20545144</v>
       </c>
       <c r="AN22" s="3">
-        <v>0.141700342297554</v>
+        <v>0.14170034</v>
       </c>
       <c r="AO22" s="3">
-        <v>0.5397446751594543</v>
+        <v>0.5397447</v>
       </c>
       <c r="AP22" s="3">
-        <v>0.8153713345527649</v>
+        <v>0.8153713299999999</v>
       </c>
       <c r="AQ22" s="3">
-        <v>0.9994693994522095</v>
+        <v>0.9994694</v>
       </c>
       <c r="AR22" s="3">
-        <v>0.6984915733337402</v>
+        <v>0.6984916</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.9212164878845215</v>
+        <v>0.9212165</v>
       </c>
       <c r="AT22" s="3">
-        <v>0.7371706366539001</v>
+        <v>0.73717064</v>
       </c>
       <c r="AU22" s="3">
-        <v>-4.748846530914307</v>
+        <v>-4.7488465</v>
       </c>
       <c r="AV22" s="3">
-        <v>66.95512390136719</v>
+        <v>66.955124</v>
       </c>
       <c r="AW22" s="3">
-        <v>13.07573509216309</v>
+        <v>13.075735</v>
       </c>
       <c r="AX22" s="3">
         <v>380.5360000000003</v>
       </c>
       <c r="AY22" s="3">
-        <v>2.756200000000002</v>
+        <v>2.756200000000001</v>
       </c>
       <c r="AZ22" s="3">
         <v>0.5948429402681562</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="AA23" s="3">
-        <v>13.9767484664917</v>
+        <v>13.976748</v>
       </c>
       <c r="AB23" s="3">
-        <v>18.78242874145508</v>
+        <v>18.782429</v>
       </c>
       <c r="AC23" s="3">
-        <v>47.19872665405273</v>
+        <v>47.198727</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
@@ -6606,55 +6606,55 @@
         <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.3301149904727936</v>
+        <v>0.330115</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.6918383240699768</v>
+        <v>0.6918383</v>
       </c>
       <c r="AI23" s="3">
-        <v>0.3266380727291107</v>
+        <v>0.32663807</v>
       </c>
       <c r="AJ23" s="3">
-        <v>0.07641936838626862</v>
+        <v>0.07641937</v>
       </c>
       <c r="AK23" s="3">
-        <v>0.932951807975769</v>
+        <v>0.9329518</v>
       </c>
       <c r="AL23" s="3">
-        <v>0.121549941599369</v>
+        <v>0.12154994</v>
       </c>
       <c r="AM23" s="3">
-        <v>0.1518135368824005</v>
+        <v>0.15181354</v>
       </c>
       <c r="AN23" s="3">
-        <v>0.1074975952506065</v>
+        <v>0.107497595</v>
       </c>
       <c r="AO23" s="3">
-        <v>0.5825311541557312</v>
+        <v>0.58253115</v>
       </c>
       <c r="AP23" s="3">
-        <v>0.7518149614334106</v>
+        <v>0.75181496</v>
       </c>
       <c r="AQ23" s="3">
-        <v>0.9995641708374023</v>
+        <v>0.9995642</v>
       </c>
       <c r="AR23" s="3">
-        <v>0.6848759055137634</v>
+        <v>0.6848759</v>
       </c>
       <c r="AS23" s="3">
-        <v>0.9149495363235474</v>
+        <v>0.91494954</v>
       </c>
       <c r="AT23" s="3">
-        <v>0.6838979721069336</v>
+        <v>0.683898</v>
       </c>
       <c r="AU23" s="3">
-        <v>-4.79519510269165</v>
+        <v>-4.795195</v>
       </c>
       <c r="AV23" s="3">
-        <v>57.78833770751953</v>
+        <v>57.788338</v>
       </c>
       <c r="AW23" s="3">
-        <v>14.3100757598877</v>
+        <v>14.310076</v>
       </c>
       <c r="AX23" s="3">
         <v>380.5360000000003</v>
@@ -6761,7 +6761,7 @@
         <v>-3.999814735548187</v>
       </c>
       <c r="Y24" s="3">
-        <v>0.0001000426678166251</v>
+        <v>0.0001000426678166</v>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="AA24" s="3">
-        <v>-4.70445728302002</v>
+        <v>-4.7044573</v>
       </c>
       <c r="AB24" s="3">
-        <v>6.318691730499268</v>
+        <v>6.3186917</v>
       </c>
       <c r="AC24" s="3">
-        <v>47.63880157470703</v>
+        <v>47.6388</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -6787,55 +6787,55 @@
         <v>1</v>
       </c>
       <c r="AG24" s="3">
-        <v>0.3792183995246887</v>
+        <v>0.3792184</v>
       </c>
       <c r="AH24" s="3">
-        <v>0.6779707670211792</v>
+        <v>0.6779707699999999</v>
       </c>
       <c r="AI24" s="3">
-        <v>0.3295310437679291</v>
+        <v>0.32953104</v>
       </c>
       <c r="AJ24" s="3">
-        <v>0.08602991700172424</v>
+        <v>0.08602992</v>
       </c>
       <c r="AK24" s="3">
-        <v>0.9211298823356628</v>
+        <v>0.9211298999999999</v>
       </c>
       <c r="AL24" s="3">
-        <v>0.1122885942459106</v>
+        <v>0.112288594</v>
       </c>
       <c r="AM24" s="3">
-        <v>0.1256495714187622</v>
+        <v>0.12564957</v>
       </c>
       <c r="AN24" s="3">
-        <v>0.07452833652496338</v>
+        <v>0.07452834</v>
       </c>
       <c r="AO24" s="3">
-        <v>0.5432442426681519</v>
+        <v>0.54324424</v>
       </c>
       <c r="AP24" s="3">
-        <v>0.6584850549697876</v>
+        <v>0.65848505</v>
       </c>
       <c r="AQ24" s="3">
-        <v>0.9987505078315735</v>
+        <v>0.9987505</v>
       </c>
       <c r="AR24" s="3">
-        <v>0.701579213142395</v>
+        <v>0.7015792</v>
       </c>
       <c r="AS24" s="3">
-        <v>0.8786209225654602</v>
+        <v>0.8786209</v>
       </c>
       <c r="AT24" s="3">
-        <v>0.6176344156265259</v>
+        <v>0.6176344</v>
       </c>
       <c r="AU24" s="3">
-        <v>-4.825148582458496</v>
+        <v>-4.8251486</v>
       </c>
       <c r="AV24" s="3">
-        <v>55.20851516723633</v>
+        <v>55.208515</v>
       </c>
       <c r="AW24" s="3">
-        <v>13.52863311767578</v>
+        <v>13.528633</v>
       </c>
       <c r="AX24" s="3">
         <v>366.5090000000002</v>
@@ -6844,7 +6844,7 @@
         <v>2.3677</v>
       </c>
       <c r="AZ24" s="3">
-        <v>0.4659554732169177</v>
+        <v>0.4659554732169176</v>
       </c>
       <c r="BA24" s="3">
         <v>4</v>
@@ -6909,7 +6909,7 @@
         <v>0.3294711295316617</v>
       </c>
       <c r="N25" s="3">
-        <v>18.94834002284815</v>
+        <v>18.94834002284814</v>
       </c>
       <c r="O25" s="3">
         <v>11.50057165231426</v>
@@ -6942,7 +6942,7 @@
         <v>-4.003266281114144</v>
       </c>
       <c r="Y25" s="3">
-        <v>9.925073209232013E-05</v>
+        <v>9.925073209232012E-05</v>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="AA25" s="3">
-        <v>-13.36562061309814</v>
+        <v>-13.365621</v>
       </c>
       <c r="AB25" s="3">
-        <v>-6.608923435211182</v>
+        <v>-6.6089234</v>
       </c>
       <c r="AC25" s="3">
-        <v>42.0102653503418</v>
+        <v>42.010265</v>
       </c>
       <c r="AD25" s="3">
         <v>0</v>
@@ -6968,55 +6968,55 @@
         <v>0</v>
       </c>
       <c r="AG25" s="3">
-        <v>0.1064343228936195</v>
+        <v>0.10643432</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.3796555399894714</v>
+        <v>0.37965554</v>
       </c>
       <c r="AI25" s="3">
-        <v>0.09070359915494919</v>
+        <v>0.0907036</v>
       </c>
       <c r="AJ25" s="3">
-        <v>0.04711077362298965</v>
+        <v>0.047110774</v>
       </c>
       <c r="AK25" s="3">
-        <v>0.7416476011276245</v>
+        <v>0.7416476</v>
       </c>
       <c r="AL25" s="3">
-        <v>0.006490122526884079</v>
+        <v>0.0064901225</v>
       </c>
       <c r="AM25" s="3">
-        <v>0.01049665082246065</v>
+        <v>0.010496651</v>
       </c>
       <c r="AN25" s="3">
-        <v>0.005253965966403484</v>
+        <v>0.005253966</v>
       </c>
       <c r="AO25" s="3">
-        <v>0.2970759272575378</v>
+        <v>0.29707593</v>
       </c>
       <c r="AP25" s="3">
-        <v>0.05619137361645699</v>
+        <v>0.056191374</v>
       </c>
       <c r="AQ25" s="3">
-        <v>0.9859476089477539</v>
+        <v>0.9859476</v>
       </c>
       <c r="AR25" s="3">
-        <v>0.7711347937583923</v>
+        <v>0.7711348</v>
       </c>
       <c r="AS25" s="3">
-        <v>0.8145847320556641</v>
+        <v>0.81458473</v>
       </c>
       <c r="AT25" s="3">
-        <v>0.1156292706727982</v>
+        <v>0.11562927</v>
       </c>
       <c r="AU25" s="3">
-        <v>-4.923386573791504</v>
+        <v>-4.9233866</v>
       </c>
       <c r="AV25" s="3">
-        <v>36.17284393310547</v>
+        <v>36.172844</v>
       </c>
       <c r="AW25" s="3">
-        <v>10.83882522583008</v>
+        <v>10.838825</v>
       </c>
       <c r="AX25" s="3">
         <v>366.5090000000002</v>
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="AA26" s="3">
-        <v>11.63510131835938</v>
+        <v>11.635101</v>
       </c>
       <c r="AB26" s="3">
-        <v>12.48919677734375</v>
+        <v>12.489197</v>
       </c>
       <c r="AC26" s="3">
-        <v>45.30510711669922</v>
+        <v>45.305107</v>
       </c>
       <c r="AD26" s="3">
         <v>0</v>
@@ -7149,55 +7149,55 @@
         <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>0.2827900052070618</v>
+        <v>0.28279</v>
       </c>
       <c r="AH26" s="3">
-        <v>0.4099828600883484</v>
+        <v>0.40998286</v>
       </c>
       <c r="AI26" s="3">
-        <v>0.1270026117563248</v>
+        <v>0.12700261</v>
       </c>
       <c r="AJ26" s="3">
-        <v>0.06163079664111137</v>
+        <v>0.061630797</v>
       </c>
       <c r="AK26" s="3">
-        <v>0.8724933862686157</v>
+        <v>0.8724934</v>
       </c>
       <c r="AL26" s="3">
-        <v>0.01005907543003559</v>
+        <v>0.010059075</v>
       </c>
       <c r="AM26" s="3">
-        <v>0.02087283879518509</v>
+        <v>0.020872839</v>
       </c>
       <c r="AN26" s="3">
-        <v>0.01071572117507458</v>
+        <v>0.010715721</v>
       </c>
       <c r="AO26" s="3">
-        <v>0.2744031846523285</v>
+        <v>0.27440318</v>
       </c>
       <c r="AP26" s="3">
-        <v>0.282547652721405</v>
+        <v>0.28254765</v>
       </c>
       <c r="AQ26" s="3">
-        <v>0.9873186349868774</v>
+        <v>0.98731863</v>
       </c>
       <c r="AR26" s="3">
-        <v>0.6965105533599854</v>
+        <v>0.69651055</v>
       </c>
       <c r="AS26" s="3">
-        <v>0.8401827812194824</v>
+        <v>0.8401828</v>
       </c>
       <c r="AT26" s="3">
-        <v>0.2482448071241379</v>
+        <v>0.2482448</v>
       </c>
       <c r="AU26" s="3">
-        <v>-4.998320579528809</v>
+        <v>-4.9983206</v>
       </c>
       <c r="AV26" s="3">
-        <v>39.70697402954102</v>
+        <v>39.706974</v>
       </c>
       <c r="AW26" s="3">
-        <v>14.77231311798096</v>
+        <v>14.772313</v>
       </c>
       <c r="AX26" s="3">
         <v>423.6050000000004</v>
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="AA27" s="3">
-        <v>10.23325824737549</v>
+        <v>10.233258</v>
       </c>
       <c r="AB27" s="3">
-        <v>16.76848030090332</v>
+        <v>16.76848</v>
       </c>
       <c r="AC27" s="3">
-        <v>53.14850997924805</v>
+        <v>53.14851</v>
       </c>
       <c r="AD27" s="3">
         <v>0</v>
@@ -7330,55 +7330,55 @@
         <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>0.1076667457818985</v>
+        <v>0.107666746</v>
       </c>
       <c r="AH27" s="3">
-        <v>0.617022693157196</v>
+        <v>0.6170227</v>
       </c>
       <c r="AI27" s="3">
-        <v>0.2470436096191406</v>
+        <v>0.24704361</v>
       </c>
       <c r="AJ27" s="3">
-        <v>0.08285792171955109</v>
+        <v>0.08285792</v>
       </c>
       <c r="AK27" s="3">
-        <v>0.8627969622612</v>
+        <v>0.8627969599999999</v>
       </c>
       <c r="AL27" s="3">
-        <v>0.06041378527879715</v>
+        <v>0.060413785</v>
       </c>
       <c r="AM27" s="3">
-        <v>0.1096597760915756</v>
+        <v>0.109659776</v>
       </c>
       <c r="AN27" s="3">
-        <v>0.09576074779033661</v>
+        <v>0.09576075000000001</v>
       </c>
       <c r="AO27" s="3">
-        <v>0.5216434597969055</v>
+        <v>0.5216434599999999</v>
       </c>
       <c r="AP27" s="3">
-        <v>0.349644809961319</v>
+        <v>0.3496448</v>
       </c>
       <c r="AQ27" s="3">
-        <v>0.9995976686477661</v>
+        <v>0.99959767</v>
       </c>
       <c r="AR27" s="3">
-        <v>0.7183729410171509</v>
+        <v>0.71837294</v>
       </c>
       <c r="AS27" s="3">
-        <v>0.8623026013374329</v>
+        <v>0.8623026</v>
       </c>
       <c r="AT27" s="3">
-        <v>0.3700311183929443</v>
+        <v>0.37003112</v>
       </c>
       <c r="AU27" s="3">
-        <v>-5.026082515716553</v>
+        <v>-5.0260825</v>
       </c>
       <c r="AV27" s="3">
-        <v>72.19638824462891</v>
+        <v>72.19638999999999</v>
       </c>
       <c r="AW27" s="3">
-        <v>18.12118911743164</v>
+        <v>18.12119</v>
       </c>
       <c r="AX27" s="3">
         <v>366.5090000000003</v>
@@ -7393,7 +7393,7 @@
         <v>4</v>
       </c>
       <c r="BB27" s="3">
-        <v>3.299268677727794</v>
+        <v>3.299268677727793</v>
       </c>
       <c r="BC27" s="3">
         <v>0.7445257024746896</v>
@@ -7485,7 +7485,7 @@
         <v>-4.003266281114144</v>
       </c>
       <c r="Y28" s="3">
-        <v>9.925073209232013E-05</v>
+        <v>9.925073209232012E-05</v>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="AA28" s="3">
-        <v>2.867519378662109</v>
+        <v>2.8675194</v>
       </c>
       <c r="AB28" s="3">
-        <v>11.35608100891113</v>
+        <v>11.356081</v>
       </c>
       <c r="AC28" s="3">
-        <v>40.93791961669922</v>
+        <v>40.93792</v>
       </c>
       <c r="AD28" s="3">
         <v>0</v>
@@ -7511,55 +7511,55 @@
         <v>0</v>
       </c>
       <c r="AG28" s="3">
-        <v>0.283047616481781</v>
+        <v>0.28304762</v>
       </c>
       <c r="AH28" s="3">
-        <v>0.6519478559494019</v>
+        <v>0.65194786</v>
       </c>
       <c r="AI28" s="3">
-        <v>0.3143161237239838</v>
+        <v>0.31431612</v>
       </c>
       <c r="AJ28" s="3">
-        <v>0.07918323576450348</v>
+        <v>0.079183236</v>
       </c>
       <c r="AK28" s="3">
-        <v>0.9127868413925171</v>
+        <v>0.91278684</v>
       </c>
       <c r="AL28" s="3">
-        <v>0.1055863276124001</v>
+        <v>0.10558633</v>
       </c>
       <c r="AM28" s="3">
-        <v>0.1389849632978439</v>
+        <v>0.13898496</v>
       </c>
       <c r="AN28" s="3">
-        <v>0.0957830399274826</v>
+        <v>0.09578304</v>
       </c>
       <c r="AO28" s="3">
-        <v>0.5203244090080261</v>
+        <v>0.5203244</v>
       </c>
       <c r="AP28" s="3">
-        <v>0.6533122062683105</v>
+        <v>0.6533122</v>
       </c>
       <c r="AQ28" s="3">
-        <v>0.999367356300354</v>
+        <v>0.99936736</v>
       </c>
       <c r="AR28" s="3">
-        <v>0.7064558863639832</v>
+        <v>0.7064559</v>
       </c>
       <c r="AS28" s="3">
-        <v>0.8961795568466187</v>
+        <v>0.89617956</v>
       </c>
       <c r="AT28" s="3">
-        <v>0.5761261582374573</v>
+        <v>0.5761261600000001</v>
       </c>
       <c r="AU28" s="3">
-        <v>-4.781678676605225</v>
+        <v>-4.7816787</v>
       </c>
       <c r="AV28" s="3">
-        <v>55.96059417724609</v>
+        <v>55.960594</v>
       </c>
       <c r="AW28" s="3">
-        <v>11.81860733032227</v>
+        <v>11.818607</v>
       </c>
       <c r="AX28" s="3">
         <v>366.5090000000002</v>
@@ -7666,7 +7666,7 @@
         <v>-5.017860410077316</v>
       </c>
       <c r="Y29" s="3">
-        <v>9.597090493992333E-06</v>
+        <v>9.597090493992331E-06</v>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
@@ -7674,13 +7674,13 @@
         </is>
       </c>
       <c r="AA29" s="3">
-        <v>5.289857387542725</v>
+        <v>5.2898574</v>
       </c>
       <c r="AB29" s="3">
-        <v>-0.5652084350585938</v>
+        <v>-0.56520844</v>
       </c>
       <c r="AC29" s="3">
-        <v>46.54450988769531</v>
+        <v>46.54451</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -7692,55 +7692,55 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
-        <v>0.06748171150684357</v>
+        <v>0.06748171</v>
       </c>
       <c r="AH29" s="3">
-        <v>0.6617470979690552</v>
+        <v>0.6617471</v>
       </c>
       <c r="AI29" s="3">
-        <v>0.5297685861587524</v>
+        <v>0.5297686</v>
       </c>
       <c r="AJ29" s="3">
-        <v>0.08345480263233185</v>
+        <v>0.0834548</v>
       </c>
       <c r="AK29" s="3">
-        <v>0.9244734644889832</v>
+        <v>0.92447346</v>
       </c>
       <c r="AL29" s="3">
-        <v>0.1626725941896439</v>
+        <v>0.1626726</v>
       </c>
       <c r="AM29" s="3">
-        <v>0.2639357149600983</v>
+        <v>0.26393571</v>
       </c>
       <c r="AN29" s="3">
-        <v>0.4509312510490417</v>
+        <v>0.45093125</v>
       </c>
       <c r="AO29" s="3">
-        <v>0.4670811593532562</v>
+        <v>0.46708116</v>
       </c>
       <c r="AP29" s="3">
-        <v>0.9106627702713013</v>
+        <v>0.9106628</v>
       </c>
       <c r="AQ29" s="3">
-        <v>0.9998321533203125</v>
+        <v>0.99983215</v>
       </c>
       <c r="AR29" s="3">
-        <v>0.7499046325683594</v>
+        <v>0.74990463</v>
       </c>
       <c r="AS29" s="3">
-        <v>0.8881341814994812</v>
+        <v>0.8881342</v>
       </c>
       <c r="AT29" s="3">
-        <v>0.7560857534408569</v>
+        <v>0.75608575</v>
       </c>
       <c r="AU29" s="3">
-        <v>-5.246415138244629</v>
+        <v>-5.246415</v>
       </c>
       <c r="AV29" s="3">
-        <v>77.00187683105469</v>
+        <v>77.00188</v>
       </c>
       <c r="AW29" s="3">
-        <v>13.67186546325684</v>
+        <v>13.671865</v>
       </c>
       <c r="AX29" s="3">
         <v>429.5680000000002</v>
@@ -7847,7 +7847,7 @@
         <v>-3.974666289610127</v>
       </c>
       <c r="Y30" s="3">
-        <v>0.0001060067964894961</v>
+        <v>0.0001060067964894</v>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
@@ -7855,13 +7855,13 @@
         </is>
       </c>
       <c r="AA30" s="3">
-        <v>-3.175653457641602</v>
+        <v>-3.1756535</v>
       </c>
       <c r="AB30" s="3">
-        <v>4.78775691986084</v>
+        <v>4.787757</v>
       </c>
       <c r="AC30" s="3">
-        <v>42.97135543823242</v>
+        <v>42.971355</v>
       </c>
       <c r="AD30" s="3">
         <v>0</v>
@@ -7873,55 +7873,55 @@
         <v>0</v>
       </c>
       <c r="AG30" s="3">
-        <v>0.1125938445329666</v>
+        <v>0.112593845</v>
       </c>
       <c r="AH30" s="3">
-        <v>0.409783661365509</v>
+        <v>0.40978366</v>
       </c>
       <c r="AI30" s="3">
-        <v>0.542510986328125</v>
+        <v>0.542511</v>
       </c>
       <c r="AJ30" s="3">
-        <v>0.04599837586283684</v>
+        <v>0.045998376</v>
       </c>
       <c r="AK30" s="3">
-        <v>0.6010975241661072</v>
+        <v>0.6010975</v>
       </c>
       <c r="AL30" s="3">
-        <v>0.03148866817355156</v>
+        <v>0.03148867</v>
       </c>
       <c r="AM30" s="3">
-        <v>0.1200100630521774</v>
+        <v>0.12001006</v>
       </c>
       <c r="AN30" s="3">
-        <v>0.1500450819730759</v>
+        <v>0.15004508</v>
       </c>
       <c r="AO30" s="3">
-        <v>0.0605962947010994</v>
+        <v>0.060596295</v>
       </c>
       <c r="AP30" s="3">
-        <v>0.3523684144020081</v>
+        <v>0.3523684</v>
       </c>
       <c r="AQ30" s="3">
-        <v>0.9996474385261536</v>
+        <v>0.9996474400000001</v>
       </c>
       <c r="AR30" s="3">
-        <v>0.8594871759414673</v>
+        <v>0.8594872</v>
       </c>
       <c r="AS30" s="3">
-        <v>0.8984431028366089</v>
+        <v>0.8984431000000001</v>
       </c>
       <c r="AT30" s="3">
-        <v>0.2951036393642426</v>
+        <v>0.29510364</v>
       </c>
       <c r="AU30" s="3">
-        <v>-5.383204936981201</v>
+        <v>-5.383205</v>
       </c>
       <c r="AV30" s="3">
-        <v>62.66500854492188</v>
+        <v>62.66501</v>
       </c>
       <c r="AW30" s="3">
-        <v>16.69514083862305</v>
+        <v>16.69514</v>
       </c>
       <c r="AX30" s="3">
         <v>383.4920000000003</v>
@@ -8016,7 +8016,7 @@
         <v>3.563023183376728</v>
       </c>
       <c r="U31" s="3">
-        <v>5.699493250352043</v>
+        <v>5.699493250352044</v>
       </c>
       <c r="V31" s="3">
         <v>0.5450178742283966</v>
@@ -8036,13 +8036,13 @@
         </is>
       </c>
       <c r="AA31" s="3">
-        <v>3.408648014068604</v>
+        <v>3.408648</v>
       </c>
       <c r="AB31" s="3">
-        <v>13.89355945587158</v>
+        <v>13.893559</v>
       </c>
       <c r="AC31" s="3">
-        <v>45.84992218017578</v>
+        <v>45.849922</v>
       </c>
       <c r="AD31" s="3">
         <v>0</v>
@@ -8054,58 +8054,58 @@
         <v>0</v>
       </c>
       <c r="AG31" s="3">
-        <v>0.1724347323179245</v>
+        <v>0.17243473</v>
       </c>
       <c r="AH31" s="3">
-        <v>0.4835044741630554</v>
+        <v>0.48350447</v>
       </c>
       <c r="AI31" s="3">
-        <v>0.4768244624137878</v>
+        <v>0.47682446</v>
       </c>
       <c r="AJ31" s="3">
-        <v>0.04047805815935135</v>
+        <v>0.04047806</v>
       </c>
       <c r="AK31" s="3">
-        <v>0.6552438139915466</v>
+        <v>0.6552438</v>
       </c>
       <c r="AL31" s="3">
-        <v>0.01765371486544609</v>
+        <v>0.017653715</v>
       </c>
       <c r="AM31" s="3">
-        <v>0.06120733171701431</v>
+        <v>0.06120733</v>
       </c>
       <c r="AN31" s="3">
-        <v>0.0846514105796814</v>
+        <v>0.08465141</v>
       </c>
       <c r="AO31" s="3">
-        <v>0.05866561084985733</v>
+        <v>0.05866561</v>
       </c>
       <c r="AP31" s="3">
-        <v>0.4316245019435883</v>
+        <v>0.4316245</v>
       </c>
       <c r="AQ31" s="3">
-        <v>0.9993988275527954</v>
+        <v>0.9993988</v>
       </c>
       <c r="AR31" s="3">
-        <v>0.8395342826843262</v>
+        <v>0.8395343</v>
       </c>
       <c r="AS31" s="3">
-        <v>0.874114990234375</v>
+        <v>0.874115</v>
       </c>
       <c r="AT31" s="3">
-        <v>0.3391581177711487</v>
+        <v>0.33915812</v>
       </c>
       <c r="AU31" s="3">
-        <v>-5.318098545074463</v>
+        <v>-5.3180985</v>
       </c>
       <c r="AV31" s="3">
-        <v>60.87032318115234</v>
+        <v>60.870323</v>
       </c>
       <c r="AW31" s="3">
-        <v>18.53779029846191</v>
+        <v>18.53779</v>
       </c>
       <c r="AX31" s="3">
-        <v>397.5190000000003</v>
+        <v>397.5190000000004</v>
       </c>
       <c r="AY31" s="3">
         <v>2.567700000000001</v>
@@ -8194,7 +8194,7 @@
         <v>435.0775523834791</v>
       </c>
       <c r="T32" s="3">
-        <v>3.361433323343635</v>
+        <v>3.361433323343636</v>
       </c>
       <c r="U32" s="3">
         <v>5.740740490554029</v>
@@ -8217,13 +8217,13 @@
         </is>
       </c>
       <c r="AA32" s="3">
-        <v>-8.98122501373291</v>
+        <v>-8.981225</v>
       </c>
       <c r="AB32" s="3">
-        <v>-4.455055236816406</v>
+        <v>-4.455055</v>
       </c>
       <c r="AC32" s="3">
-        <v>78.04102325439453</v>
+        <v>78.04102</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -8235,55 +8235,55 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>0.2788024246692657</v>
+        <v>0.27880242</v>
       </c>
       <c r="AH32" s="3">
-        <v>0.6779440641403198</v>
+        <v>0.67794406</v>
       </c>
       <c r="AI32" s="3">
-        <v>0.6910129189491272</v>
+        <v>0.6910129</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0.09135498106479645</v>
+        <v>0.09135498</v>
       </c>
       <c r="AK32" s="3">
-        <v>0.7887123823165894</v>
+        <v>0.7887124</v>
       </c>
       <c r="AL32" s="3">
-        <v>0.04875016957521439</v>
+        <v>0.04875017</v>
       </c>
       <c r="AM32" s="3">
-        <v>0.0747484415769577</v>
+        <v>0.07474844</v>
       </c>
       <c r="AN32" s="3">
-        <v>0.1606288850307465</v>
+        <v>0.16062889</v>
       </c>
       <c r="AO32" s="3">
-        <v>0.1485177874565125</v>
+        <v>0.14851779</v>
       </c>
       <c r="AP32" s="3">
-        <v>0.5451629757881165</v>
+        <v>0.545163</v>
       </c>
       <c r="AQ32" s="3">
-        <v>0.9699270129203796</v>
+        <v>0.969927</v>
       </c>
       <c r="AR32" s="3">
-        <v>0.8076591491699219</v>
+        <v>0.80765915</v>
       </c>
       <c r="AS32" s="3">
-        <v>0.5796800255775452</v>
+        <v>0.57968</v>
       </c>
       <c r="AT32" s="3">
-        <v>0.5443651676177979</v>
+        <v>0.54436517</v>
       </c>
       <c r="AU32" s="3">
-        <v>-5.332209587097168</v>
+        <v>-5.3322096</v>
       </c>
       <c r="AV32" s="3">
-        <v>78.45448303222656</v>
+        <v>78.45448</v>
       </c>
       <c r="AW32" s="3">
-        <v>22.51340103149414</v>
+        <v>22.513401</v>
       </c>
       <c r="AX32" s="3">
         <v>433.5560000000002</v>
@@ -8351,7 +8351,7 @@
         <v>5.373630949798338</v>
       </c>
       <c r="L33" s="3">
-        <v>1.366420734972021</v>
+        <v>1.36642073497202</v>
       </c>
       <c r="M33" s="3">
         <v>0.6148213696040044</v>
@@ -8398,13 +8398,13 @@
         </is>
       </c>
       <c r="AA33" s="3">
-        <v>-11.67121505737305</v>
+        <v>-11.671215</v>
       </c>
       <c r="AB33" s="3">
-        <v>-9.258498191833496</v>
+        <v>-9.258497999999999</v>
       </c>
       <c r="AC33" s="3">
-        <v>53.88170623779297</v>
+        <v>53.881706</v>
       </c>
       <c r="AD33" s="3">
         <v>0</v>
@@ -8416,55 +8416,55 @@
         <v>0</v>
       </c>
       <c r="AG33" s="3">
-        <v>0.06627894192934036</v>
+        <v>0.06627893999999999</v>
       </c>
       <c r="AH33" s="3">
-        <v>0.3814792037010193</v>
+        <v>0.3814792</v>
       </c>
       <c r="AI33" s="3">
-        <v>0.1230860725045204</v>
+        <v>0.12308607</v>
       </c>
       <c r="AJ33" s="3">
-        <v>0.0561656653881073</v>
+        <v>0.056165665</v>
       </c>
       <c r="AK33" s="3">
-        <v>0.6620650291442871</v>
+        <v>0.662065</v>
       </c>
       <c r="AL33" s="3">
-        <v>0.004520400427281857</v>
+        <v>0.0045204004</v>
       </c>
       <c r="AM33" s="3">
-        <v>0.01158264186233282</v>
+        <v>0.011582642</v>
       </c>
       <c r="AN33" s="3">
-        <v>0.008014448918402195</v>
+        <v>0.008014449</v>
       </c>
       <c r="AO33" s="3">
-        <v>0.2504454255104065</v>
+        <v>0.25044543</v>
       </c>
       <c r="AP33" s="3">
-        <v>0.03570348769426346</v>
+        <v>0.035703488</v>
       </c>
       <c r="AQ33" s="3">
-        <v>0.9743517637252808</v>
+        <v>0.97435176</v>
       </c>
       <c r="AR33" s="3">
-        <v>0.7235878705978394</v>
+        <v>0.7235879</v>
       </c>
       <c r="AS33" s="3">
-        <v>0.586004912853241</v>
+        <v>0.5860049000000001</v>
       </c>
       <c r="AT33" s="3">
-        <v>0.08717197179794312</v>
+        <v>0.08717197</v>
       </c>
       <c r="AU33" s="3">
-        <v>-5.281462669372559</v>
+        <v>-5.2814627</v>
       </c>
       <c r="AV33" s="3">
-        <v>57.2914924621582</v>
+        <v>57.291492</v>
       </c>
       <c r="AW33" s="3">
-        <v>16.36507415771484</v>
+        <v>16.365074</v>
       </c>
       <c r="AX33" s="3">
         <v>381.5240000000003</v>
@@ -8538,7 +8538,7 @@
         <v>0.67219475221375</v>
       </c>
       <c r="N34" s="3">
-        <v>54.75753462688252</v>
+        <v>54.75753462688253</v>
       </c>
       <c r="O34" s="3">
         <v>74.0236875285066</v>
@@ -8579,13 +8579,13 @@
         </is>
       </c>
       <c r="AA34" s="3">
-        <v>-27.22682189941406</v>
+        <v>-27.226822</v>
       </c>
       <c r="AB34" s="3">
-        <v>-13.89472007751465</v>
+        <v>-13.89472</v>
       </c>
       <c r="AC34" s="3">
-        <v>45.28893280029297</v>
+        <v>45.288933</v>
       </c>
       <c r="AD34" s="3">
         <v>0</v>
@@ -8597,55 +8597,55 @@
         <v>0</v>
       </c>
       <c r="AG34" s="3">
-        <v>0.3304834961891174</v>
+        <v>0.3304835</v>
       </c>
       <c r="AH34" s="3">
-        <v>0.6352441310882568</v>
+        <v>0.63524413</v>
       </c>
       <c r="AI34" s="3">
-        <v>0.778465211391449</v>
+        <v>0.7784652</v>
       </c>
       <c r="AJ34" s="3">
-        <v>0.1573345512151718</v>
+        <v>0.15733455</v>
       </c>
       <c r="AK34" s="3">
-        <v>0.5338507890701294</v>
+        <v>0.5338508</v>
       </c>
       <c r="AL34" s="3">
-        <v>0.05925401300191879</v>
+        <v>0.059254013</v>
       </c>
       <c r="AM34" s="3">
-        <v>0.07537920773029327</v>
+        <v>0.07537921</v>
       </c>
       <c r="AN34" s="3">
-        <v>0.1283094733953476</v>
+        <v>0.12830947</v>
       </c>
       <c r="AO34" s="3">
-        <v>0.108478918671608</v>
+        <v>0.10847892</v>
       </c>
       <c r="AP34" s="3">
-        <v>0.1564613580703735</v>
+        <v>0.15646136</v>
       </c>
       <c r="AQ34" s="3">
-        <v>0.8154527544975281</v>
+        <v>0.8154527499999999</v>
       </c>
       <c r="AR34" s="3">
-        <v>0.8039594888687134</v>
+        <v>0.8039595</v>
       </c>
       <c r="AS34" s="3">
-        <v>0.2377715557813644</v>
+        <v>0.23777156</v>
       </c>
       <c r="AT34" s="3">
-        <v>0.2734041810035706</v>
+        <v>0.27340418</v>
       </c>
       <c r="AU34" s="3">
-        <v>-5.476291656494141</v>
+        <v>-5.4762917</v>
       </c>
       <c r="AV34" s="3">
-        <v>78.49551391601562</v>
+        <v>78.495514</v>
       </c>
       <c r="AW34" s="3">
-        <v>7.442433834075928</v>
+        <v>7.442434</v>
       </c>
       <c r="AX34" s="3">
         <v>432.5240000000002</v>
@@ -8760,13 +8760,13 @@
         </is>
       </c>
       <c r="AA35" s="3">
-        <v>31.7279167175293</v>
+        <v>31.727917</v>
       </c>
       <c r="AB35" s="3">
-        <v>17.85879516601562</v>
+        <v>17.858795</v>
       </c>
       <c r="AC35" s="3">
-        <v>45.68531036376953</v>
+        <v>45.68531</v>
       </c>
       <c r="AD35" s="3">
         <v>0</v>
@@ -8778,55 +8778,55 @@
         <v>0</v>
       </c>
       <c r="AG35" s="3">
-        <v>0.1225418224930763</v>
+        <v>0.12254182</v>
       </c>
       <c r="AH35" s="3">
-        <v>0.4609773755073547</v>
+        <v>0.46097738</v>
       </c>
       <c r="AI35" s="3">
-        <v>0.8749173879623413</v>
+        <v>0.8749174</v>
       </c>
       <c r="AJ35" s="3">
-        <v>0.07076207548379898</v>
+        <v>0.07076207499999999</v>
       </c>
       <c r="AK35" s="3">
-        <v>0.8881179094314575</v>
+        <v>0.8881179</v>
       </c>
       <c r="AL35" s="3">
-        <v>0.2259233444929123</v>
+        <v>0.22592334</v>
       </c>
       <c r="AM35" s="3">
-        <v>0.4093533158302307</v>
+        <v>0.40935332</v>
       </c>
       <c r="AN35" s="3">
-        <v>0.7644366025924683</v>
+        <v>0.7644366</v>
       </c>
       <c r="AO35" s="3">
-        <v>0.1123594865202904</v>
+        <v>0.11235949</v>
       </c>
       <c r="AP35" s="3">
-        <v>0.9650079607963562</v>
+        <v>0.96500796</v>
       </c>
       <c r="AQ35" s="3">
-        <v>0.9998376965522766</v>
+        <v>0.9998377000000001</v>
       </c>
       <c r="AR35" s="3">
-        <v>0.8320387601852417</v>
+        <v>0.83203876</v>
       </c>
       <c r="AS35" s="3">
-        <v>0.9161101579666138</v>
+        <v>0.91611016</v>
       </c>
       <c r="AT35" s="3">
-        <v>0.8967151641845703</v>
+        <v>0.89671516</v>
       </c>
       <c r="AU35" s="3">
-        <v>-5.200964450836182</v>
+        <v>-5.2009645</v>
       </c>
       <c r="AV35" s="3">
-        <v>92.53944396972656</v>
+        <v>92.539444</v>
       </c>
       <c r="AW35" s="3">
-        <v>9.354611396789551</v>
+        <v>9.354611</v>
       </c>
       <c r="AX35" s="3">
         <v>444.5350000000002</v>
@@ -8912,7 +8912,7 @@
         <v>0.585284972797344</v>
       </c>
       <c r="R36" s="3">
-        <v>1.813963065257415</v>
+        <v>1.813963065257414</v>
       </c>
       <c r="S36" s="3">
         <v>357.2280339166194</v>
@@ -8941,13 +8941,13 @@
         </is>
       </c>
       <c r="AA36" s="3">
-        <v>35.00133514404297</v>
+        <v>35.001335</v>
       </c>
       <c r="AB36" s="3">
-        <v>15.03205108642578</v>
+        <v>15.032051</v>
       </c>
       <c r="AC36" s="3">
-        <v>49.3444709777832</v>
+        <v>49.34447</v>
       </c>
       <c r="AD36" s="3">
         <v>0</v>
@@ -8959,55 +8959,55 @@
         <v>0</v>
       </c>
       <c r="AG36" s="3">
-        <v>0.1763534396886826</v>
+        <v>0.17635344</v>
       </c>
       <c r="AH36" s="3">
-        <v>0.5100067257881165</v>
+        <v>0.5100067</v>
       </c>
       <c r="AI36" s="3">
-        <v>0.9058307409286499</v>
+        <v>0.90583074</v>
       </c>
       <c r="AJ36" s="3">
-        <v>0.1023280471563339</v>
+        <v>0.10232805</v>
       </c>
       <c r="AK36" s="3">
-        <v>0.8607792854309082</v>
+        <v>0.8607793</v>
       </c>
       <c r="AL36" s="3">
-        <v>0.3278890252113342</v>
+        <v>0.32788903</v>
       </c>
       <c r="AM36" s="3">
-        <v>0.3343397974967957</v>
+        <v>0.3343398</v>
       </c>
       <c r="AN36" s="3">
-        <v>0.7132730484008789</v>
+        <v>0.71327305</v>
       </c>
       <c r="AO36" s="3">
-        <v>0.09852404892444611</v>
+        <v>0.09852405</v>
       </c>
       <c r="AP36" s="3">
-        <v>0.9312259554862976</v>
+        <v>0.93122596</v>
       </c>
       <c r="AQ36" s="3">
-        <v>0.999660313129425</v>
+        <v>0.9996602999999999</v>
       </c>
       <c r="AR36" s="3">
-        <v>0.8638860583305359</v>
+        <v>0.86388606</v>
       </c>
       <c r="AS36" s="3">
-        <v>0.9080005884170532</v>
+        <v>0.9080006</v>
       </c>
       <c r="AT36" s="3">
-        <v>0.8609592318534851</v>
+        <v>0.86095923</v>
       </c>
       <c r="AU36" s="3">
-        <v>-5.22114086151123</v>
+        <v>-5.221141</v>
       </c>
       <c r="AV36" s="3">
-        <v>96.06053924560547</v>
+        <v>96.06054</v>
       </c>
       <c r="AW36" s="3">
-        <v>7.968595027923584</v>
+        <v>7.968595</v>
       </c>
       <c r="AX36" s="3">
         <v>444.5350000000001</v>
@@ -9093,7 +9093,7 @@
         <v>0.7731715736272672</v>
       </c>
       <c r="R37" s="3">
-        <v>0.3898589281544764</v>
+        <v>0.3898589281544763</v>
       </c>
       <c r="S37" s="3">
         <v>418.5429712567586</v>
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="AA37" s="3">
-        <v>18.36164474487305</v>
+        <v>18.361645</v>
       </c>
       <c r="AB37" s="3">
-        <v>8.63557243347168</v>
+        <v>8.635572</v>
       </c>
       <c r="AC37" s="3">
-        <v>40.10017013549805</v>
+        <v>40.10017</v>
       </c>
       <c r="AD37" s="3">
         <v>0</v>
@@ -9140,55 +9140,55 @@
         <v>0</v>
       </c>
       <c r="AG37" s="3">
-        <v>0.1764194369316101</v>
+        <v>0.17641944</v>
       </c>
       <c r="AH37" s="3">
-        <v>0.3717483878135681</v>
+        <v>0.3717484</v>
       </c>
       <c r="AI37" s="3">
-        <v>0.921978771686554</v>
+        <v>0.9219788</v>
       </c>
       <c r="AJ37" s="3">
-        <v>0.07752425968647003</v>
+        <v>0.07752426</v>
       </c>
       <c r="AK37" s="3">
-        <v>0.6954941153526306</v>
+        <v>0.6954941</v>
       </c>
       <c r="AL37" s="3">
-        <v>0.1809723973274231</v>
+        <v>0.1809724</v>
       </c>
       <c r="AM37" s="3">
-        <v>0.2043587267398834</v>
+        <v>0.20435873</v>
       </c>
       <c r="AN37" s="3">
-        <v>0.4661042094230652</v>
+        <v>0.4661042</v>
       </c>
       <c r="AO37" s="3">
-        <v>0.03625907376408577</v>
+        <v>0.036259074</v>
       </c>
       <c r="AP37" s="3">
-        <v>0.8239345550537109</v>
+        <v>0.82393456</v>
       </c>
       <c r="AQ37" s="3">
-        <v>0.9995524287223816</v>
+        <v>0.9995524</v>
       </c>
       <c r="AR37" s="3">
-        <v>0.8769677877426147</v>
+        <v>0.8769678</v>
       </c>
       <c r="AS37" s="3">
-        <v>0.8854867815971375</v>
+        <v>0.8854868</v>
       </c>
       <c r="AT37" s="3">
-        <v>0.501103401184082</v>
+        <v>0.5011034</v>
       </c>
       <c r="AU37" s="3">
-        <v>-4.964478969573975</v>
+        <v>-4.964479</v>
       </c>
       <c r="AV37" s="3">
-        <v>90.50892639160156</v>
+        <v>90.50893000000001</v>
       </c>
       <c r="AW37" s="3">
-        <v>7.270132541656494</v>
+        <v>7.2701325</v>
       </c>
       <c r="AX37" s="3">
         <v>432.4800000000002</v>
@@ -9259,7 +9259,7 @@
         <v>1.100529824691589</v>
       </c>
       <c r="M38" s="3">
-        <v>0.2789982894027183</v>
+        <v>0.2789982894027182</v>
       </c>
       <c r="N38" s="3">
         <v>15.1457796042164</v>
@@ -9271,7 +9271,7 @@
         <v>4.899470175308411</v>
       </c>
       <c r="Q38" s="3">
-        <v>0.2789982894027183</v>
+        <v>0.2789982894027182</v>
       </c>
       <c r="R38" s="3">
         <v>3.578435366863939</v>
@@ -9286,7 +9286,7 @@
         <v>5.446306822537739</v>
       </c>
       <c r="V38" s="3">
-        <v>0.2789982894027183</v>
+        <v>0.2789982894027182</v>
       </c>
       <c r="W38" s="3">
         <v>3.070600000000002</v>
@@ -9303,13 +9303,13 @@
         </is>
       </c>
       <c r="AA38" s="3">
-        <v>15.59116077423096</v>
+        <v>15.591161</v>
       </c>
       <c r="AB38" s="3">
-        <v>22.65704727172852</v>
+        <v>22.657047</v>
       </c>
       <c r="AC38" s="3">
-        <v>42.06156539916992</v>
+        <v>42.061565</v>
       </c>
       <c r="AD38" s="3">
         <v>0</v>
@@ -9321,55 +9321,55 @@
         <v>0</v>
       </c>
       <c r="AG38" s="3">
-        <v>0.2633714079856873</v>
+        <v>0.2633714</v>
       </c>
       <c r="AH38" s="3">
-        <v>0.445606529712677</v>
+        <v>0.44560653</v>
       </c>
       <c r="AI38" s="3">
-        <v>0.4436851441860199</v>
+        <v>0.44368514</v>
       </c>
       <c r="AJ38" s="3">
-        <v>0.03461447358131409</v>
+        <v>0.034614474</v>
       </c>
       <c r="AK38" s="3">
-        <v>0.7959173917770386</v>
+        <v>0.7959174</v>
       </c>
       <c r="AL38" s="3">
-        <v>0.0322757288813591</v>
+        <v>0.03227573</v>
       </c>
       <c r="AM38" s="3">
-        <v>0.1025429368019104</v>
+        <v>0.10254294</v>
       </c>
       <c r="AN38" s="3">
-        <v>0.1840361654758453</v>
+        <v>0.18403617</v>
       </c>
       <c r="AO38" s="3">
-        <v>0.134496659040451</v>
+        <v>0.13449666</v>
       </c>
       <c r="AP38" s="3">
-        <v>0.8487926721572876</v>
+        <v>0.8487927</v>
       </c>
       <c r="AQ38" s="3">
-        <v>0.9991857409477234</v>
+        <v>0.99918574</v>
       </c>
       <c r="AR38" s="3">
-        <v>0.6797599792480469</v>
+        <v>0.67976</v>
       </c>
       <c r="AS38" s="3">
-        <v>0.8617540597915649</v>
+        <v>0.86175406</v>
       </c>
       <c r="AT38" s="3">
-        <v>0.7050368189811707</v>
+        <v>0.7050368</v>
       </c>
       <c r="AU38" s="3">
-        <v>-4.741759300231934</v>
+        <v>-4.7417593</v>
       </c>
       <c r="AV38" s="3">
-        <v>82.50645446777344</v>
+        <v>82.50645400000001</v>
       </c>
       <c r="AW38" s="3">
-        <v>11.07054328918457</v>
+        <v>11.070543</v>
       </c>
       <c r="AX38" s="3">
         <v>407.5580000000003</v>
@@ -9484,13 +9484,13 @@
         </is>
       </c>
       <c r="AA39" s="3">
-        <v>14.10036659240723</v>
+        <v>14.100367</v>
       </c>
       <c r="AB39" s="3">
-        <v>-4.575030326843262</v>
+        <v>-4.5750303</v>
       </c>
       <c r="AC39" s="3">
-        <v>60.98880767822266</v>
+        <v>60.988808</v>
       </c>
       <c r="AD39" s="3">
         <v>0</v>
@@ -9502,55 +9502,55 @@
         <v>0</v>
       </c>
       <c r="AG39" s="3">
-        <v>0.09151919186115265</v>
+        <v>0.09151919</v>
       </c>
       <c r="AH39" s="3">
-        <v>0.612733006477356</v>
+        <v>0.612733</v>
       </c>
       <c r="AI39" s="3">
-        <v>0.893536388874054</v>
+        <v>0.8935364</v>
       </c>
       <c r="AJ39" s="3">
-        <v>0.09572348743677139</v>
+        <v>0.09572348999999999</v>
       </c>
       <c r="AK39" s="3">
-        <v>0.8596595525741577</v>
+        <v>0.8596595500000001</v>
       </c>
       <c r="AL39" s="3">
-        <v>0.2467740029096603</v>
+        <v>0.246774</v>
       </c>
       <c r="AM39" s="3">
-        <v>0.2413970977067947</v>
+        <v>0.2413971</v>
       </c>
       <c r="AN39" s="3">
-        <v>0.6468733549118042</v>
+        <v>0.64687335</v>
       </c>
       <c r="AO39" s="3">
-        <v>0.1159836873412132</v>
+        <v>0.11598369</v>
       </c>
       <c r="AP39" s="3">
-        <v>0.897899329662323</v>
+        <v>0.8978993</v>
       </c>
       <c r="AQ39" s="3">
-        <v>0.9991679191589355</v>
+        <v>0.9991679</v>
       </c>
       <c r="AR39" s="3">
-        <v>0.8581619262695312</v>
+        <v>0.8581619</v>
       </c>
       <c r="AS39" s="3">
-        <v>0.8518335223197937</v>
+        <v>0.8518335</v>
       </c>
       <c r="AT39" s="3">
-        <v>0.8054553270339966</v>
+        <v>0.8054553</v>
       </c>
       <c r="AU39" s="3">
-        <v>-5.517002105712891</v>
+        <v>-5.517002</v>
       </c>
       <c r="AV39" s="3">
-        <v>87.20699310302734</v>
+        <v>87.20699</v>
       </c>
       <c r="AW39" s="3">
-        <v>12.52952289581299</v>
+        <v>12.529523</v>
       </c>
       <c r="AX39" s="3">
         <v>455.5620000000002</v>
@@ -9621,7 +9621,7 @@
         <v>1.302814133219174</v>
       </c>
       <c r="M40" s="3">
-        <v>0.3968168042060751</v>
+        <v>0.396816804206075</v>
       </c>
       <c r="N40" s="3">
         <v>28.32198245534405</v>
@@ -9633,7 +9633,7 @@
         <v>4.697185866780826</v>
       </c>
       <c r="Q40" s="3">
-        <v>0.3968168042060751</v>
+        <v>0.396816804206075</v>
       </c>
       <c r="R40" s="3">
         <v>3.350064717758045</v>
@@ -9648,7 +9648,7 @@
         <v>5.474946803024733</v>
       </c>
       <c r="V40" s="3">
-        <v>0.3968168042060751</v>
+        <v>0.396816804206075</v>
       </c>
       <c r="W40" s="3">
         <v>2.44</v>
@@ -9665,13 +9665,13 @@
         </is>
       </c>
       <c r="AA40" s="3">
-        <v>11.72569751739502</v>
+        <v>11.7256975</v>
       </c>
       <c r="AB40" s="3">
-        <v>-6.051044464111328</v>
+        <v>-6.0510445</v>
       </c>
       <c r="AC40" s="3">
-        <v>57.50371170043945</v>
+        <v>57.50371</v>
       </c>
       <c r="AD40" s="3">
         <v>0</v>
@@ -9683,55 +9683,55 @@
         <v>0</v>
       </c>
       <c r="AG40" s="3">
-        <v>0.1325110346078873</v>
+        <v>0.13251103</v>
       </c>
       <c r="AH40" s="3">
-        <v>0.5538431406021118</v>
+        <v>0.55384314</v>
       </c>
       <c r="AI40" s="3">
-        <v>0.9050809144973755</v>
+        <v>0.9050809</v>
       </c>
       <c r="AJ40" s="3">
-        <v>0.08572937548160553</v>
+        <v>0.085729375</v>
       </c>
       <c r="AK40" s="3">
-        <v>0.7529138326644897</v>
+        <v>0.75291383</v>
       </c>
       <c r="AL40" s="3">
-        <v>0.1143219918012619</v>
+        <v>0.11432199</v>
       </c>
       <c r="AM40" s="3">
-        <v>0.1315694451332092</v>
+        <v>0.13156945</v>
       </c>
       <c r="AN40" s="3">
-        <v>0.3818269371986389</v>
+        <v>0.38182694</v>
       </c>
       <c r="AO40" s="3">
-        <v>0.05529382079839706</v>
+        <v>0.05529382</v>
       </c>
       <c r="AP40" s="3">
-        <v>0.7371336221694946</v>
+        <v>0.7371336000000001</v>
       </c>
       <c r="AQ40" s="3">
-        <v>0.9976369142532349</v>
+        <v>0.9976369</v>
       </c>
       <c r="AR40" s="3">
-        <v>0.8765016794204712</v>
+        <v>0.8765017000000001</v>
       </c>
       <c r="AS40" s="3">
-        <v>0.7603046298027039</v>
+        <v>0.76030463</v>
       </c>
       <c r="AT40" s="3">
-        <v>0.5513055920600891</v>
+        <v>0.5513056</v>
       </c>
       <c r="AU40" s="3">
-        <v>-5.480358600616455</v>
+        <v>-5.4803586</v>
       </c>
       <c r="AV40" s="3">
-        <v>85.04900360107422</v>
+        <v>85.04900000000001</v>
       </c>
       <c r="AW40" s="3">
-        <v>11.54821872711182</v>
+        <v>11.548219</v>
       </c>
       <c r="AX40" s="3">
         <v>441.5350000000002</v>
@@ -9805,7 +9805,7 @@
         <v>0.4201576735263461</v>
       </c>
       <c r="N41" s="3">
-        <v>31.05571532108434</v>
+        <v>31.05571532108433</v>
       </c>
       <c r="O41" s="3">
         <v>22.58689636369687</v>
@@ -9832,7 +9832,7 @@
         <v>0.4201576735263461</v>
       </c>
       <c r="W41" s="3">
-        <v>2.380179999999999</v>
+        <v>2.38018</v>
       </c>
       <c r="X41" s="3">
         <v>-4.847380528805034</v>
@@ -9846,13 +9846,13 @@
         </is>
       </c>
       <c r="AA41" s="3">
-        <v>-5.332494735717773</v>
+        <v>-5.3324947</v>
       </c>
       <c r="AB41" s="3">
-        <v>-3.550041198730469</v>
+        <v>-3.5500412</v>
       </c>
       <c r="AC41" s="3">
-        <v>47.68855285644531</v>
+        <v>47.688553</v>
       </c>
       <c r="AD41" s="3">
         <v>0</v>
@@ -9864,61 +9864,61 @@
         <v>0</v>
       </c>
       <c r="AG41" s="3">
-        <v>0.1783537268638611</v>
+        <v>0.17835373</v>
       </c>
       <c r="AH41" s="3">
-        <v>0.6844334602355957</v>
+        <v>0.68443346</v>
       </c>
       <c r="AI41" s="3">
-        <v>0.7644474506378174</v>
+        <v>0.76444745</v>
       </c>
       <c r="AJ41" s="3">
-        <v>0.04944724217057228</v>
+        <v>0.049447242</v>
       </c>
       <c r="AK41" s="3">
-        <v>0.8718268275260925</v>
+        <v>0.8718268</v>
       </c>
       <c r="AL41" s="3">
-        <v>0.02590401843190193</v>
+        <v>0.025904018</v>
       </c>
       <c r="AM41" s="3">
-        <v>0.06888151913881302</v>
+        <v>0.06888152</v>
       </c>
       <c r="AN41" s="3">
-        <v>0.2349500954151154</v>
+        <v>0.2349501</v>
       </c>
       <c r="AO41" s="3">
-        <v>0.09186498075723648</v>
+        <v>0.09186498</v>
       </c>
       <c r="AP41" s="3">
-        <v>0.8152786493301392</v>
+        <v>0.81527865</v>
       </c>
       <c r="AQ41" s="3">
-        <v>0.9946386218070984</v>
+        <v>0.9946386</v>
       </c>
       <c r="AR41" s="3">
-        <v>0.8486016392707825</v>
+        <v>0.84860164</v>
       </c>
       <c r="AS41" s="3">
-        <v>0.7050008177757263</v>
+        <v>0.7050008</v>
       </c>
       <c r="AT41" s="3">
-        <v>0.6588881611824036</v>
+        <v>0.6588881599999999</v>
       </c>
       <c r="AU41" s="3">
-        <v>-5.638335704803467</v>
+        <v>-5.6383357</v>
       </c>
       <c r="AV41" s="3">
-        <v>71.90293884277344</v>
+        <v>71.90294</v>
       </c>
       <c r="AW41" s="3">
-        <v>13.78930854797363</v>
+        <v>13.789309</v>
       </c>
       <c r="AX41" s="3">
         <v>486.6200000000004</v>
       </c>
       <c r="AY41" s="3">
-        <v>2.380179999999999</v>
+        <v>2.38018</v>
       </c>
       <c r="AZ41" s="3">
         <v>0.3373031556368657</v>
@@ -9980,13 +9980,13 @@
         <v>5.311369211361228</v>
       </c>
       <c r="L42" s="3">
-        <v>1.313989859088271</v>
+        <v>1.313989859088272</v>
       </c>
       <c r="M42" s="3">
         <v>0.4457447271114641</v>
       </c>
       <c r="N42" s="3">
-        <v>31.79855585992835</v>
+        <v>31.79855585992836</v>
       </c>
       <c r="O42" s="3">
         <v>24.26990153557899</v>
@@ -10027,13 +10027,13 @@
         </is>
       </c>
       <c r="AA42" s="3">
-        <v>18.24996376037598</v>
+        <v>18.249964</v>
       </c>
       <c r="AB42" s="3">
-        <v>2.23211932182312</v>
+        <v>2.2321193</v>
       </c>
       <c r="AC42" s="3">
-        <v>46.5171012878418</v>
+        <v>46.5171</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -10045,55 +10045,55 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
-        <v>0.1523607075214386</v>
+        <v>0.15236071</v>
       </c>
       <c r="AH42" s="3">
-        <v>0.6061654090881348</v>
+        <v>0.6061654</v>
       </c>
       <c r="AI42" s="3">
-        <v>0.9022954106330872</v>
+        <v>0.9022954</v>
       </c>
       <c r="AJ42" s="3">
-        <v>0.1028810143470764</v>
+        <v>0.102881014</v>
       </c>
       <c r="AK42" s="3">
-        <v>0.8041078448295593</v>
+        <v>0.80410784</v>
       </c>
       <c r="AL42" s="3">
-        <v>0.2023194283246994</v>
+        <v>0.20231943</v>
       </c>
       <c r="AM42" s="3">
-        <v>0.1471401751041412</v>
+        <v>0.14714018</v>
       </c>
       <c r="AN42" s="3">
-        <v>0.4111798703670502</v>
+        <v>0.41117987</v>
       </c>
       <c r="AO42" s="3">
-        <v>0.08587388694286346</v>
+        <v>0.08587388999999999</v>
       </c>
       <c r="AP42" s="3">
-        <v>0.7422569990158081</v>
+        <v>0.7422569999999999</v>
       </c>
       <c r="AQ42" s="3">
-        <v>0.9979561567306519</v>
+        <v>0.99795616</v>
       </c>
       <c r="AR42" s="3">
-        <v>0.8900570869445801</v>
+        <v>0.8900571</v>
       </c>
       <c r="AS42" s="3">
-        <v>0.8088762164115906</v>
+        <v>0.8088762</v>
       </c>
       <c r="AT42" s="3">
-        <v>0.5528427362442017</v>
+        <v>0.55284274</v>
       </c>
       <c r="AU42" s="3">
-        <v>-5.385034084320068</v>
+        <v>-5.385034</v>
       </c>
       <c r="AV42" s="3">
-        <v>90.69264984130859</v>
+        <v>90.69265</v>
       </c>
       <c r="AW42" s="3">
-        <v>6.370079040527344</v>
+        <v>6.370079</v>
       </c>
       <c r="AX42" s="3">
         <v>441.5350000000003</v>
@@ -10208,13 +10208,13 @@
         </is>
       </c>
       <c r="AA43" s="3">
-        <v>22.77546882629395</v>
+        <v>22.775469</v>
       </c>
       <c r="AB43" s="3">
-        <v>7.230002403259277</v>
+        <v>7.2300024</v>
       </c>
       <c r="AC43" s="3">
-        <v>40.92090225219727</v>
+        <v>40.920902</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -10226,55 +10226,55 @@
         <v>0</v>
       </c>
       <c r="AG43" s="3">
-        <v>0.07428675144910812</v>
+        <v>0.07428675</v>
       </c>
       <c r="AH43" s="3">
-        <v>0.5022108554840088</v>
+        <v>0.50221086</v>
       </c>
       <c r="AI43" s="3">
-        <v>0.869240939617157</v>
+        <v>0.86924094</v>
       </c>
       <c r="AJ43" s="3">
-        <v>0.06343580782413483</v>
+        <v>0.06343581</v>
       </c>
       <c r="AK43" s="3">
-        <v>0.8877205848693848</v>
+        <v>0.8877206</v>
       </c>
       <c r="AL43" s="3">
-        <v>0.1343493163585663</v>
+        <v>0.13434932</v>
       </c>
       <c r="AM43" s="3">
-        <v>0.3053164482116699</v>
+        <v>0.30531645</v>
       </c>
       <c r="AN43" s="3">
-        <v>0.7024456262588501</v>
+        <v>0.7024456</v>
       </c>
       <c r="AO43" s="3">
-        <v>0.09783134609460831</v>
+        <v>0.097831346</v>
       </c>
       <c r="AP43" s="3">
-        <v>0.9683369398117065</v>
+        <v>0.96833694</v>
       </c>
       <c r="AQ43" s="3">
-        <v>0.9998294115066528</v>
+        <v>0.9998294</v>
       </c>
       <c r="AR43" s="3">
-        <v>0.8538644909858704</v>
+        <v>0.8538645</v>
       </c>
       <c r="AS43" s="3">
-        <v>0.8918484449386597</v>
+        <v>0.89184844</v>
       </c>
       <c r="AT43" s="3">
-        <v>0.8549380302429199</v>
+        <v>0.85493803</v>
       </c>
       <c r="AU43" s="3">
-        <v>-5.339334964752197</v>
+        <v>-5.339335</v>
       </c>
       <c r="AV43" s="3">
-        <v>87.59556579589844</v>
+        <v>87.59556600000001</v>
       </c>
       <c r="AW43" s="3">
-        <v>9.271635055541992</v>
+        <v>9.271635</v>
       </c>
       <c r="AX43" s="3">
         <v>455.5620000000002</v>
@@ -10389,13 +10389,13 @@
         </is>
       </c>
       <c r="AA44" s="3">
-        <v>25.49727821350098</v>
+        <v>25.497278</v>
       </c>
       <c r="AB44" s="3">
-        <v>19.60936546325684</v>
+        <v>19.609365</v>
       </c>
       <c r="AC44" s="3">
-        <v>53.04461669921875</v>
+        <v>53.044617</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -10407,55 +10407,55 @@
         <v>0</v>
       </c>
       <c r="AG44" s="3">
-        <v>0.1224256530404091</v>
+        <v>0.12242565</v>
       </c>
       <c r="AH44" s="3">
-        <v>0.3158243298530579</v>
+        <v>0.31582433</v>
       </c>
       <c r="AI44" s="3">
-        <v>0.8805713653564453</v>
+        <v>0.88057137</v>
       </c>
       <c r="AJ44" s="3">
-        <v>0.08310658484697342</v>
+        <v>0.083106585</v>
       </c>
       <c r="AK44" s="3">
-        <v>0.7687126398086548</v>
+        <v>0.7687126399999999</v>
       </c>
       <c r="AL44" s="3">
-        <v>0.4877883791923523</v>
+        <v>0.48778838</v>
       </c>
       <c r="AM44" s="3">
-        <v>0.6015079617500305</v>
+        <v>0.60150796</v>
       </c>
       <c r="AN44" s="3">
-        <v>0.826743483543396</v>
+        <v>0.8267435</v>
       </c>
       <c r="AO44" s="3">
-        <v>0.174489364027977</v>
+        <v>0.17448936</v>
       </c>
       <c r="AP44" s="3">
-        <v>0.9604833722114563</v>
+        <v>0.9604834</v>
       </c>
       <c r="AQ44" s="3">
-        <v>0.9999516606330872</v>
+        <v>0.99995166</v>
       </c>
       <c r="AR44" s="3">
-        <v>0.7229530811309814</v>
+        <v>0.7229531</v>
       </c>
       <c r="AS44" s="3">
-        <v>0.9341449737548828</v>
+        <v>0.934145</v>
       </c>
       <c r="AT44" s="3">
-        <v>0.7442425489425659</v>
+        <v>0.7442425499999999</v>
       </c>
       <c r="AU44" s="3">
-        <v>-5.024964332580566</v>
+        <v>-5.0249643</v>
       </c>
       <c r="AV44" s="3">
-        <v>95.56005859375</v>
+        <v>95.56005999999999</v>
       </c>
       <c r="AW44" s="3">
-        <v>9.714588165283203</v>
+        <v>9.714587999999999</v>
       </c>
       <c r="AX44" s="3">
         <v>426.5240000000002</v>
@@ -10541,7 +10541,7 @@
         <v>0.2909847366302437</v>
       </c>
       <c r="R45" s="3">
-        <v>3.606929966877899</v>
+        <v>3.606929966877898</v>
       </c>
       <c r="S45" s="3">
         <v>49.86523586466451</v>
@@ -10570,13 +10570,13 @@
         </is>
       </c>
       <c r="AA45" s="3">
-        <v>23.95201110839844</v>
+        <v>23.952011</v>
       </c>
       <c r="AB45" s="3">
-        <v>35.92058181762695</v>
+        <v>35.92058</v>
       </c>
       <c r="AC45" s="3">
-        <v>56.07839202880859</v>
+        <v>56.078392</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -10588,55 +10588,55 @@
         <v>0</v>
       </c>
       <c r="AG45" s="3">
-        <v>0.1894308179616928</v>
+        <v>0.18943082</v>
       </c>
       <c r="AH45" s="3">
-        <v>0.1707205772399902</v>
+        <v>0.17072058</v>
       </c>
       <c r="AI45" s="3">
-        <v>0.9105633497238159</v>
+        <v>0.91056335</v>
       </c>
       <c r="AJ45" s="3">
-        <v>0.07235898822546005</v>
+        <v>0.07235899</v>
       </c>
       <c r="AK45" s="3">
-        <v>0.6140678524971008</v>
+        <v>0.61406785</v>
       </c>
       <c r="AL45" s="3">
-        <v>0.2974019050598145</v>
+        <v>0.2974019</v>
       </c>
       <c r="AM45" s="3">
-        <v>0.4617322981357574</v>
+        <v>0.4617323</v>
       </c>
       <c r="AN45" s="3">
-        <v>0.6654883623123169</v>
+        <v>0.66548836</v>
       </c>
       <c r="AO45" s="3">
-        <v>0.03441900014877319</v>
+        <v>0.034419</v>
       </c>
       <c r="AP45" s="3">
-        <v>0.831049919128418</v>
+        <v>0.8310499</v>
       </c>
       <c r="AQ45" s="3">
-        <v>0.9996212720870972</v>
+        <v>0.9996213</v>
       </c>
       <c r="AR45" s="3">
-        <v>0.8229900598526001</v>
+        <v>0.82299006</v>
       </c>
       <c r="AS45" s="3">
-        <v>0.9333900213241577</v>
+        <v>0.9333900000000001</v>
       </c>
       <c r="AT45" s="3">
-        <v>0.7486408352851868</v>
+        <v>0.74864084</v>
       </c>
       <c r="AU45" s="3">
-        <v>-4.454654693603516</v>
+        <v>-4.4546547</v>
       </c>
       <c r="AV45" s="3">
-        <v>94.95288848876953</v>
+        <v>94.95289</v>
       </c>
       <c r="AW45" s="3">
-        <v>8.122148513793945</v>
+        <v>8.1221485</v>
       </c>
       <c r="AX45" s="3">
         <v>370.4560000000002</v>
@@ -10710,7 +10710,7 @@
         <v>0.3517481792166991</v>
       </c>
       <c r="N46" s="3">
-        <v>22.76865622930166</v>
+        <v>22.76865622930165</v>
       </c>
       <c r="O46" s="3">
         <v>15.80795604763821</v>
@@ -10743,7 +10743,7 @@
         <v>-4.003998001629259</v>
       </c>
       <c r="Y46" s="3">
-        <v>9.908365041358763E-05</v>
+        <v>9.908365041358764E-05</v>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
@@ -10751,13 +10751,13 @@
         </is>
       </c>
       <c r="AA46" s="3">
-        <v>-6.443224430084229</v>
+        <v>-6.4432244</v>
       </c>
       <c r="AB46" s="3">
-        <v>5.785635948181152</v>
+        <v>5.785636</v>
       </c>
       <c r="AC46" s="3">
-        <v>42.76530838012695</v>
+        <v>42.76531</v>
       </c>
       <c r="AD46" s="3">
         <v>0</v>
@@ -10769,55 +10769,55 @@
         <v>0</v>
       </c>
       <c r="AG46" s="3">
-        <v>0.1415677815675735</v>
+        <v>0.14156778</v>
       </c>
       <c r="AH46" s="3">
-        <v>0.4993196129798889</v>
+        <v>0.4993196</v>
       </c>
       <c r="AI46" s="3">
-        <v>0.8566528558731079</v>
+        <v>0.85665286</v>
       </c>
       <c r="AJ46" s="3">
-        <v>0.06345143169164658</v>
+        <v>0.06345143</v>
       </c>
       <c r="AK46" s="3">
-        <v>0.7109256386756897</v>
+        <v>0.71092564</v>
       </c>
       <c r="AL46" s="3">
-        <v>0.1272261142730713</v>
+        <v>0.12722611</v>
       </c>
       <c r="AM46" s="3">
-        <v>0.09035879373550415</v>
+        <v>0.09035879400000001</v>
       </c>
       <c r="AN46" s="3">
-        <v>0.2765695452690125</v>
+        <v>0.27656955</v>
       </c>
       <c r="AO46" s="3">
-        <v>0.04202980548143387</v>
+        <v>0.042029805</v>
       </c>
       <c r="AP46" s="3">
-        <v>0.7534851431846619</v>
+        <v>0.75348514</v>
       </c>
       <c r="AQ46" s="3">
-        <v>0.9979823231697083</v>
+        <v>0.9979823</v>
       </c>
       <c r="AR46" s="3">
-        <v>0.8839862942695618</v>
+        <v>0.8839863</v>
       </c>
       <c r="AS46" s="3">
-        <v>0.8224831819534302</v>
+        <v>0.8224832</v>
       </c>
       <c r="AT46" s="3">
-        <v>0.4635264873504639</v>
+        <v>0.4635265</v>
       </c>
       <c r="AU46" s="3">
-        <v>-4.765597820281982</v>
+        <v>-4.765598</v>
       </c>
       <c r="AV46" s="3">
-        <v>75.08123779296875</v>
+        <v>75.08123999999999</v>
       </c>
       <c r="AW46" s="3">
-        <v>8.161409378051758</v>
+        <v>8.161409000000001</v>
       </c>
       <c r="AX46" s="3">
         <v>371.4440000000001</v>
@@ -10932,13 +10932,13 @@
         </is>
       </c>
       <c r="AA47" s="3">
-        <v>-6.803152561187744</v>
+        <v>-6.8031526</v>
       </c>
       <c r="AB47" s="3">
-        <v>10.1956787109375</v>
+        <v>10.195679</v>
       </c>
       <c r="AC47" s="3">
-        <v>63.71723175048828</v>
+        <v>63.71723</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -10950,55 +10950,55 @@
         <v>0</v>
       </c>
       <c r="AG47" s="3">
-        <v>0.2939130663871765</v>
+        <v>0.29391307</v>
       </c>
       <c r="AH47" s="3">
-        <v>0.4678744375705719</v>
+        <v>0.46787444</v>
       </c>
       <c r="AI47" s="3">
-        <v>0.8451622724533081</v>
+        <v>0.8451623</v>
       </c>
       <c r="AJ47" s="3">
-        <v>0.07766401767730713</v>
+        <v>0.07766402</v>
       </c>
       <c r="AK47" s="3">
-        <v>0.6647903919219971</v>
+        <v>0.6647904</v>
       </c>
       <c r="AL47" s="3">
-        <v>0.06813132017850876</v>
+        <v>0.06813132</v>
       </c>
       <c r="AM47" s="3">
-        <v>0.06616445630788803</v>
+        <v>0.06616445999999999</v>
       </c>
       <c r="AN47" s="3">
-        <v>0.1550951898097992</v>
+        <v>0.15509519</v>
       </c>
       <c r="AO47" s="3">
-        <v>0.03442123532295227</v>
+        <v>0.034421235</v>
       </c>
       <c r="AP47" s="3">
-        <v>0.4871956408023834</v>
+        <v>0.48719564</v>
       </c>
       <c r="AQ47" s="3">
-        <v>0.9942492246627808</v>
+        <v>0.9942492000000001</v>
       </c>
       <c r="AR47" s="3">
-        <v>0.8748952150344849</v>
+        <v>0.8748952</v>
       </c>
       <c r="AS47" s="3">
-        <v>0.8102601766586304</v>
+        <v>0.8102602</v>
       </c>
       <c r="AT47" s="3">
-        <v>0.5465739369392395</v>
+        <v>0.54657394</v>
       </c>
       <c r="AU47" s="3">
-        <v>-4.497586727142334</v>
+        <v>-4.4975867</v>
       </c>
       <c r="AV47" s="3">
-        <v>84.24427795410156</v>
+        <v>84.24428</v>
       </c>
       <c r="AW47" s="3">
-        <v>10.52753353118896</v>
+        <v>10.527534</v>
       </c>
       <c r="AX47" s="3">
         <v>370.4560000000001</v>
@@ -11075,7 +11075,7 @@
         <v>18.275014152428</v>
       </c>
       <c r="O48" s="3">
-        <v>10.00105058060877</v>
+        <v>10.00105058060878</v>
       </c>
       <c r="P48" s="3">
         <v>4.823051633806064</v>
@@ -11113,13 +11113,13 @@
         </is>
       </c>
       <c r="AA48" s="3">
-        <v>-4.760066032409668</v>
+        <v>-4.760066</v>
       </c>
       <c r="AB48" s="3">
-        <v>12.09438419342041</v>
+        <v>12.094384</v>
       </c>
       <c r="AC48" s="3">
-        <v>60.32749557495117</v>
+        <v>60.327496</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -11131,55 +11131,55 @@
         <v>0</v>
       </c>
       <c r="AG48" s="3">
-        <v>0.267641693353653</v>
+        <v>0.2676417</v>
       </c>
       <c r="AH48" s="3">
-        <v>0.4858331680297852</v>
+        <v>0.48583317</v>
       </c>
       <c r="AI48" s="3">
-        <v>0.8327080011367798</v>
+        <v>0.832708</v>
       </c>
       <c r="AJ48" s="3">
-        <v>0.07551970332860947</v>
+        <v>0.0755197</v>
       </c>
       <c r="AK48" s="3">
-        <v>0.7091904282569885</v>
+        <v>0.7091904</v>
       </c>
       <c r="AL48" s="3">
-        <v>0.130507230758667</v>
+        <v>0.13050723</v>
       </c>
       <c r="AM48" s="3">
-        <v>0.09800741821527481</v>
+        <v>0.09800742</v>
       </c>
       <c r="AN48" s="3">
-        <v>0.2130728662014008</v>
+        <v>0.21307287</v>
       </c>
       <c r="AO48" s="3">
-        <v>0.04777613654732704</v>
+        <v>0.047776137</v>
       </c>
       <c r="AP48" s="3">
-        <v>0.6241751909255981</v>
+        <v>0.6241752</v>
       </c>
       <c r="AQ48" s="3">
-        <v>0.9965387582778931</v>
+        <v>0.99653876</v>
       </c>
       <c r="AR48" s="3">
-        <v>0.8777279853820801</v>
+        <v>0.877728</v>
       </c>
       <c r="AS48" s="3">
-        <v>0.8593435287475586</v>
+        <v>0.8593435</v>
       </c>
       <c r="AT48" s="3">
-        <v>0.5867623090744019</v>
+        <v>0.5867623</v>
       </c>
       <c r="AU48" s="3">
-        <v>-4.480303287506104</v>
+        <v>-4.4803033</v>
       </c>
       <c r="AV48" s="3">
-        <v>84.66037750244141</v>
+        <v>84.66038</v>
       </c>
       <c r="AW48" s="3">
-        <v>9.882367134094238</v>
+        <v>9.882367</v>
       </c>
       <c r="AX48" s="3">
         <v>370.4560000000001</v>
@@ -11294,13 +11294,13 @@
         </is>
       </c>
       <c r="AA49" s="3">
-        <v>28.91144752502441</v>
+        <v>28.911448</v>
       </c>
       <c r="AB49" s="3">
-        <v>46.95753860473633</v>
+        <v>46.95754</v>
       </c>
       <c r="AC49" s="3">
-        <v>48.4306640625</v>
+        <v>48.430664</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -11312,55 +11312,55 @@
         <v>0</v>
       </c>
       <c r="AG49" s="3">
-        <v>0.13190658390522</v>
+        <v>0.13190658</v>
       </c>
       <c r="AH49" s="3">
-        <v>0.1497708708047867</v>
+        <v>0.14977087</v>
       </c>
       <c r="AI49" s="3">
-        <v>0.8880643844604492</v>
+        <v>0.8880644</v>
       </c>
       <c r="AJ49" s="3">
-        <v>0.05179054662585258</v>
+        <v>0.051790547</v>
       </c>
       <c r="AK49" s="3">
-        <v>0.7019727230072021</v>
+        <v>0.7019727</v>
       </c>
       <c r="AL49" s="3">
-        <v>0.3156796991825104</v>
+        <v>0.3156797</v>
       </c>
       <c r="AM49" s="3">
-        <v>0.6714868545532227</v>
+        <v>0.67148685</v>
       </c>
       <c r="AN49" s="3">
-        <v>0.8176481127738953</v>
+        <v>0.8176481</v>
       </c>
       <c r="AO49" s="3">
-        <v>0.05277041345834732</v>
+        <v>0.052770413</v>
       </c>
       <c r="AP49" s="3">
-        <v>0.9346717596054077</v>
+        <v>0.93467176</v>
       </c>
       <c r="AQ49" s="3">
-        <v>0.9999403953552246</v>
+        <v>0.9999404</v>
       </c>
       <c r="AR49" s="3">
-        <v>0.7528429627418518</v>
+        <v>0.7528429599999999</v>
       </c>
       <c r="AS49" s="3">
-        <v>0.9433163404464722</v>
+        <v>0.94331634</v>
       </c>
       <c r="AT49" s="3">
-        <v>0.8514154553413391</v>
+        <v>0.85141546</v>
       </c>
       <c r="AU49" s="3">
-        <v>-4.43996524810791</v>
+        <v>-4.4399652</v>
       </c>
       <c r="AV49" s="3">
-        <v>94.08110809326172</v>
+        <v>94.08111</v>
       </c>
       <c r="AW49" s="3">
-        <v>7.535311698913574</v>
+        <v>7.5353117</v>
       </c>
       <c r="AX49" s="3">
         <v>384.4830000000002</v>
@@ -11475,13 +11475,13 @@
         </is>
       </c>
       <c r="AA50" s="3">
-        <v>10.76850891113281</v>
+        <v>10.768509</v>
       </c>
       <c r="AB50" s="3">
-        <v>29.5166015625</v>
+        <v>29.516602</v>
       </c>
       <c r="AC50" s="3">
-        <v>45.05346298217773</v>
+        <v>45.053463</v>
       </c>
       <c r="AD50" s="3">
         <v>0</v>
@@ -11493,55 +11493,55 @@
         <v>0</v>
       </c>
       <c r="AG50" s="3">
-        <v>0.1589490920305252</v>
+        <v>0.15894909</v>
       </c>
       <c r="AH50" s="3">
-        <v>0.4692639410495758</v>
+        <v>0.46926394</v>
       </c>
       <c r="AI50" s="3">
-        <v>0.7488140463829041</v>
+        <v>0.74881405</v>
       </c>
       <c r="AJ50" s="3">
-        <v>0.05306855961680412</v>
+        <v>0.05306856</v>
       </c>
       <c r="AK50" s="3">
-        <v>0.8564481735229492</v>
+        <v>0.8564482</v>
       </c>
       <c r="AL50" s="3">
-        <v>0.5209315419197083</v>
+        <v>0.52093154</v>
       </c>
       <c r="AM50" s="3">
-        <v>0.5156708955764771</v>
+        <v>0.5156709</v>
       </c>
       <c r="AN50" s="3">
-        <v>0.7239679098129272</v>
+        <v>0.7239679</v>
       </c>
       <c r="AO50" s="3">
-        <v>0.1908341348171234</v>
+        <v>0.19083413</v>
       </c>
       <c r="AP50" s="3">
-        <v>0.9721763730049133</v>
+        <v>0.9721764000000001</v>
       </c>
       <c r="AQ50" s="3">
-        <v>0.9999678730964661</v>
+        <v>0.9999679</v>
       </c>
       <c r="AR50" s="3">
-        <v>0.8002592325210571</v>
+        <v>0.80025923</v>
       </c>
       <c r="AS50" s="3">
-        <v>0.9488252401351929</v>
+        <v>0.94882524</v>
       </c>
       <c r="AT50" s="3">
-        <v>0.6971380114555359</v>
+        <v>0.697138</v>
       </c>
       <c r="AU50" s="3">
-        <v>-4.792460441589355</v>
+        <v>-4.7924604</v>
       </c>
       <c r="AV50" s="3">
-        <v>80.57395935058594</v>
+        <v>80.57396</v>
       </c>
       <c r="AW50" s="3">
-        <v>13.2988920211792</v>
+        <v>13.298892</v>
       </c>
       <c r="AX50" s="3">
         <v>360.4610000000001</v>
@@ -11656,13 +11656,13 @@
         </is>
       </c>
       <c r="AA51" s="3">
-        <v>10.33920669555664</v>
+        <v>10.339207</v>
       </c>
       <c r="AB51" s="3">
-        <v>19.69132041931152</v>
+        <v>19.69132</v>
       </c>
       <c r="AC51" s="3">
-        <v>41.45897674560547</v>
+        <v>41.458977</v>
       </c>
       <c r="AD51" s="3">
         <v>0</v>
@@ -11674,55 +11674,55 @@
         <v>0</v>
       </c>
       <c r="AG51" s="3">
-        <v>0.1764541864395142</v>
+        <v>0.17645419</v>
       </c>
       <c r="AH51" s="3">
-        <v>0.5444170236587524</v>
+        <v>0.544417</v>
       </c>
       <c r="AI51" s="3">
-        <v>0.7569752931594849</v>
+        <v>0.7569753</v>
       </c>
       <c r="AJ51" s="3">
-        <v>0.09529569000005722</v>
+        <v>0.09529569</v>
       </c>
       <c r="AK51" s="3">
-        <v>0.7797631025314331</v>
+        <v>0.7797631</v>
       </c>
       <c r="AL51" s="3">
-        <v>0.2705928683280945</v>
+        <v>0.27059287</v>
       </c>
       <c r="AM51" s="3">
-        <v>0.2075865268707275</v>
+        <v>0.20758653</v>
       </c>
       <c r="AN51" s="3">
-        <v>0.3878408074378967</v>
+        <v>0.3878408</v>
       </c>
       <c r="AO51" s="3">
-        <v>0.1449253261089325</v>
+        <v>0.14492533</v>
       </c>
       <c r="AP51" s="3">
-        <v>0.7905210256576538</v>
+        <v>0.790521</v>
       </c>
       <c r="AQ51" s="3">
-        <v>0.9990707635879517</v>
+        <v>0.9990707599999999</v>
       </c>
       <c r="AR51" s="3">
-        <v>0.8375703096389771</v>
+        <v>0.8375703</v>
       </c>
       <c r="AS51" s="3">
-        <v>0.8721070289611816</v>
+        <v>0.872107</v>
       </c>
       <c r="AT51" s="3">
-        <v>0.5479071140289307</v>
+        <v>0.5479071</v>
       </c>
       <c r="AU51" s="3">
-        <v>-4.96942663192749</v>
+        <v>-4.9694266</v>
       </c>
       <c r="AV51" s="3">
-        <v>89.13878631591797</v>
+        <v>89.13879</v>
       </c>
       <c r="AW51" s="3">
-        <v>11.29797458648682</v>
+        <v>11.297975</v>
       </c>
       <c r="AX51" s="3">
         <v>375.4760000000001</v>
@@ -11837,13 +11837,13 @@
         </is>
       </c>
       <c r="AA52" s="3">
-        <v>5.601995944976807</v>
+        <v>5.601996</v>
       </c>
       <c r="AB52" s="3">
-        <v>15.37870216369629</v>
+        <v>15.378702</v>
       </c>
       <c r="AC52" s="3">
-        <v>42.64384460449219</v>
+        <v>42.643845</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -11855,55 +11855,55 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
-        <v>0.163467600941658</v>
+        <v>0.1634676</v>
       </c>
       <c r="AH52" s="3">
-        <v>0.5802385210990906</v>
+        <v>0.5802385</v>
       </c>
       <c r="AI52" s="3">
-        <v>0.7556601166725159</v>
+        <v>0.7556600999999999</v>
       </c>
       <c r="AJ52" s="3">
-        <v>0.06175296753644943</v>
+        <v>0.061752968</v>
       </c>
       <c r="AK52" s="3">
-        <v>0.8916130065917969</v>
+        <v>0.891613</v>
       </c>
       <c r="AL52" s="3">
-        <v>0.3926360905170441</v>
+        <v>0.3926361</v>
       </c>
       <c r="AM52" s="3">
-        <v>0.416238397359848</v>
+        <v>0.4162384</v>
       </c>
       <c r="AN52" s="3">
-        <v>0.6720138192176819</v>
+        <v>0.6720138</v>
       </c>
       <c r="AO52" s="3">
-        <v>0.2526133954524994</v>
+        <v>0.2526134</v>
       </c>
       <c r="AP52" s="3">
-        <v>0.9757242202758789</v>
+        <v>0.9757242</v>
       </c>
       <c r="AQ52" s="3">
-        <v>0.9998971223831177</v>
+        <v>0.9998971</v>
       </c>
       <c r="AR52" s="3">
-        <v>0.7780221104621887</v>
+        <v>0.7780221</v>
       </c>
       <c r="AS52" s="3">
-        <v>0.9079501032829285</v>
+        <v>0.9079501</v>
       </c>
       <c r="AT52" s="3">
-        <v>0.7158886194229126</v>
+        <v>0.7158886</v>
       </c>
       <c r="AU52" s="3">
-        <v>-5.088603019714355</v>
+        <v>-5.088603</v>
       </c>
       <c r="AV52" s="3">
-        <v>85.03827667236328</v>
+        <v>85.03828</v>
       </c>
       <c r="AW52" s="3">
-        <v>12.48769092559814</v>
+        <v>12.487691</v>
       </c>
       <c r="AX52" s="3">
         <v>375.4760000000001</v>
@@ -12018,13 +12018,13 @@
         </is>
       </c>
       <c r="AA53" s="3">
-        <v>46.94696044921875</v>
+        <v>46.94696</v>
       </c>
       <c r="AB53" s="3">
-        <v>42.53715515136719</v>
+        <v>42.537155</v>
       </c>
       <c r="AC53" s="3">
-        <v>40.59553527832031</v>
+        <v>40.595535</v>
       </c>
       <c r="AD53" s="3">
         <v>0</v>
@@ -12036,55 +12036,55 @@
         <v>0</v>
       </c>
       <c r="AG53" s="3">
-        <v>0.1480308473110199</v>
+        <v>0.14803085</v>
       </c>
       <c r="AH53" s="3">
-        <v>0.2634709477424622</v>
+        <v>0.26347095</v>
       </c>
       <c r="AI53" s="3">
-        <v>0.7963535189628601</v>
+        <v>0.7963535</v>
       </c>
       <c r="AJ53" s="3">
-        <v>0.04988047108054161</v>
+        <v>0.04988047</v>
       </c>
       <c r="AK53" s="3">
-        <v>0.8161830902099609</v>
+        <v>0.8161831000000001</v>
       </c>
       <c r="AL53" s="3">
-        <v>0.4100852906703949</v>
+        <v>0.4100853</v>
       </c>
       <c r="AM53" s="3">
-        <v>0.5920408368110657</v>
+        <v>0.59204084</v>
       </c>
       <c r="AN53" s="3">
-        <v>0.7269166111946106</v>
+        <v>0.7269166</v>
       </c>
       <c r="AO53" s="3">
-        <v>0.07642458379268646</v>
+        <v>0.076424584</v>
       </c>
       <c r="AP53" s="3">
-        <v>0.98207026720047</v>
+        <v>0.98207027</v>
       </c>
       <c r="AQ53" s="3">
-        <v>0.9999844431877136</v>
+        <v>0.99998444</v>
       </c>
       <c r="AR53" s="3">
-        <v>0.7953442335128784</v>
+        <v>0.79534423</v>
       </c>
       <c r="AS53" s="3">
-        <v>0.9761411547660828</v>
+        <v>0.97614115</v>
       </c>
       <c r="AT53" s="3">
-        <v>0.7654564380645752</v>
+        <v>0.76545644</v>
       </c>
       <c r="AU53" s="3">
-        <v>-4.828463554382324</v>
+        <v>-4.8284636</v>
       </c>
       <c r="AV53" s="3">
-        <v>95.00563049316406</v>
+        <v>95.00563</v>
       </c>
       <c r="AW53" s="3">
-        <v>11.12301635742188</v>
+        <v>11.123016</v>
       </c>
       <c r="AX53" s="3">
         <v>405.5460000000001</v>
